--- a/Task2/tco-model.xlsx
+++ b/Task2/tco-model.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" r:id="rId1"/>
@@ -909,6 +909,33 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="168" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -933,51 +960,24 @@
     <xf numFmtId="164" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1011,9 +1011,10 @@
     <sheetNames>
       <sheetName val="Инструкция"/>
       <sheetName val="Допущения"/>
+      <sheetName val="TCO"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="7">
           <cell r="G7">
@@ -1205,6 +1206,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1802,10 +1804,10 @@
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="33"/>
+      <c r="C28" s="54"/>
     </row>
     <row r="29" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3016,7 +3018,7 @@
         <v>77</v>
       </c>
       <c r="C18" s="17">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>78</v>
@@ -3253,24 +3255,24 @@
     </row>
     <row r="31" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
     </row>
     <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
     </row>
     <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5902,11 +5904,11 @@
       <c r="B59" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="44">
+      <c r="E59" s="65">
         <f>J51</f>
         <v>52562134.077440001</v>
       </c>
-      <c r="F59" s="45"/>
+      <c r="F59" s="66"/>
       <c r="L59" s="12" t="s">
         <v>164</v>
       </c>
@@ -5915,11 +5917,11 @@
       <c r="B60" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="44">
+      <c r="E60" s="65">
         <f>J54</f>
         <v>55715734.077439651</v>
       </c>
-      <c r="F60" s="45"/>
+      <c r="F60" s="66"/>
       <c r="L60" s="12" t="s">
         <v>166</v>
       </c>
@@ -5928,11 +5930,11 @@
       <c r="B61" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="44">
+      <c r="E61" s="65">
         <f>J56</f>
         <v>32562612.810390696</v>
       </c>
-      <c r="F61" s="45"/>
+      <c r="F61" s="66"/>
       <c r="L61" s="12" t="s">
         <v>168</v>
       </c>
@@ -5941,11 +5943,11 @@
       <c r="B62" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="44">
+      <c r="E62" s="65">
         <f>J51/5</f>
         <v>10512426.815487999</v>
       </c>
-      <c r="F62" s="45"/>
+      <c r="F62" s="66"/>
       <c r="L62" s="12" t="s">
         <v>170</v>
       </c>
@@ -5954,11 +5956,11 @@
       <c r="B63" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="44">
+      <c r="E63" s="65">
         <f>E15/12</f>
         <v>4583.333333333333</v>
       </c>
-      <c r="F63" s="45"/>
+      <c r="F63" s="66"/>
       <c r="L63" s="12" t="s">
         <v>172</v>
       </c>
@@ -5967,11 +5969,11 @@
       <c r="B64" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="46" t="str">
+      <c r="E64" s="67" t="str">
         <f>IF(E15/12&lt;=Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>В бюджете CFO</v>
       </c>
-      <c r="F64" s="45"/>
+      <c r="F64" s="66"/>
       <c r="L64" s="12" t="s">
         <v>174</v>
       </c>
@@ -5980,11 +5982,11 @@
       <c r="B65" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="47">
+      <c r="E65" s="68">
         <f>IFERROR(J51/SUM(Допущения!$C$8:$G$8),0)</f>
         <v>1.3795835715863518</v>
       </c>
-      <c r="F65" s="45"/>
+      <c r="F65" s="66"/>
       <c r="L65" s="12" t="s">
         <v>176</v>
       </c>
@@ -5993,11 +5995,11 @@
       <c r="B66" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="47">
+      <c r="E66" s="68">
         <f>IFERROR(I51/Допущения!$G$7,0)</f>
         <v>6.8888644475733329</v>
       </c>
-      <c r="F66" s="45"/>
+      <c r="F66" s="66"/>
       <c r="L66" s="12" t="s">
         <v>178</v>
       </c>
@@ -6006,11 +6008,11 @@
       <c r="B67" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="48">
+      <c r="E67" s="69">
         <f>IFERROR(J51/SUM(Допущения!$C$10:$G$10),0)</f>
         <v>4.8926867799906917E-2</v>
       </c>
-      <c r="F67" s="45"/>
+      <c r="F67" s="66"/>
       <c r="L67" s="12" t="s">
         <v>180</v>
       </c>
@@ -6019,11 +6021,11 @@
       <c r="B68" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="49">
+      <c r="E68" s="70">
         <f>IFERROR(J15/J51,0)</f>
         <v>4.6333720163110513E-2</v>
       </c>
-      <c r="F68" s="45"/>
+      <c r="F68" s="66"/>
       <c r="L68" s="12" t="s">
         <v>182</v>
       </c>
@@ -6032,11 +6034,11 @@
       <c r="B69" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="49">
+      <c r="E69" s="70">
         <f>IFERROR(J32/J51,0)</f>
         <v>0.73638562587611633</v>
       </c>
-      <c r="F69" s="45"/>
+      <c r="F69" s="66"/>
       <c r="L69" s="12" t="s">
         <v>184</v>
       </c>
@@ -6045,71 +6047,71 @@
       <c r="B70" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="49">
+      <c r="E70" s="70">
         <f>IFERROR(J40/J51,0)</f>
         <v>6.4541148295880341E-2</v>
       </c>
-      <c r="F70" s="45"/>
+      <c r="F70" s="66"/>
       <c r="L70" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="35" t="s">
+      <c r="B72" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="54"/>
+      <c r="I72" s="54"/>
+      <c r="J72" s="54"/>
+      <c r="K72" s="54"/>
+      <c r="L72" s="54"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="36" t="s">
+      <c r="B73" s="57" t="s">
         <v>188</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="38"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="58"/>
+      <c r="E73" s="58"/>
+      <c r="F73" s="58"/>
+      <c r="G73" s="58"/>
+      <c r="H73" s="58"/>
+      <c r="I73" s="58"/>
+      <c r="J73" s="58"/>
+      <c r="K73" s="58"/>
+      <c r="L73" s="59"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="39"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="33"/>
-      <c r="L74" s="40"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="54"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="54"/>
+      <c r="K74" s="54"/>
+      <c r="L74" s="61"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="41"/>
-      <c r="C75" s="42"/>
-      <c r="D75" s="42"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="42"/>
-      <c r="H75" s="42"/>
-      <c r="I75" s="42"/>
-      <c r="J75" s="42"/>
-      <c r="K75" s="42"/>
-      <c r="L75" s="43"/>
+      <c r="B75" s="62"/>
+      <c r="C75" s="63"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="63"/>
+      <c r="F75" s="63"/>
+      <c r="G75" s="63"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="63"/>
+      <c r="J75" s="63"/>
+      <c r="K75" s="63"/>
+      <c r="L75" s="64"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7068,1864 +7070,1864 @@
   <dimension ref="B2:L1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="50" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="50" customWidth="1"/>
-    <col min="3" max="3" width="16" style="50" customWidth="1"/>
-    <col min="4" max="4" width="15" style="50" customWidth="1"/>
-    <col min="5" max="10" width="14" style="50" customWidth="1"/>
-    <col min="11" max="11" width="10" style="50" customWidth="1"/>
-    <col min="12" max="12" width="46" style="50" customWidth="1"/>
-    <col min="13" max="26" width="8.7109375" style="50" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="50"/>
+    <col min="1" max="1" width="3" style="32" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="16" style="32" customWidth="1"/>
+    <col min="4" max="4" width="15" style="32" customWidth="1"/>
+    <col min="5" max="10" width="14" style="32" customWidth="1"/>
+    <col min="11" max="11" width="10" style="32" customWidth="1"/>
+    <col min="12" max="12" width="46" style="32" customWidth="1"/>
+    <col min="13" max="26" width="8.7109375" style="32" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="32"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="85" t="s">
+      <c r="G5" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="85" t="s">
+      <c r="H5" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="85" t="s">
+      <c r="I5" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="85" t="s">
+      <c r="J5" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="85" t="s">
+      <c r="K5" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="85" t="s">
+      <c r="L5" s="51" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="83">
+      <c r="D7" s="49">
         <v>25000</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="41">
         <f t="array" ref="E7">IF($D7="","",$D7*INDEX([1]Допущения!$C$25:$G$30,MATCH($C7,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>25000</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="41">
         <f t="array" ref="F7">IF($D7="","",$D7*INDEX([1]Допущения!$C$25:$G$30,MATCH($C7,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>100000</v>
       </c>
-      <c r="G7" s="75">
+      <c r="G7" s="41">
         <f t="array" ref="G7">IF($D7="","",$D7*INDEX([1]Допущения!$C$25:$G$30,MATCH($C7,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>250000</v>
       </c>
-      <c r="H7" s="75">
+      <c r="H7" s="41">
         <f t="array" ref="H7">IF($D7="","",$D7*INDEX([1]Допущения!$C$25:$G$30,MATCH($C7,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>416666.66666666669</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="41">
         <f t="array" ref="I7">IF($D7="","",$D7*INDEX([1]Допущения!$C$25:$G$30,MATCH($C7,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>583333.33333333326</v>
       </c>
-      <c r="J7" s="75">
-        <f>SUM(E7:I7)</f>
+      <c r="J7" s="41">
+        <f t="shared" ref="J7:J14" si="0">SUM(E7:I7)</f>
         <v>1375000</v>
       </c>
-      <c r="K7" s="82"/>
-      <c r="L7" s="81" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="47" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="83">
+      <c r="D8" s="49">
         <v>24000</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="41">
         <f t="array" ref="E8">IF($D8="","",$D8*INDEX([1]Допущения!$C$25:$G$30,MATCH($C8,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>24000</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="41">
         <f t="array" ref="F8">IF($D8="","",$D8*INDEX([1]Допущения!$C$25:$G$30,MATCH($C8,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>96000</v>
       </c>
-      <c r="G8" s="75">
+      <c r="G8" s="41">
         <f t="array" ref="G8">IF($D8="","",$D8*INDEX([1]Допущения!$C$25:$G$30,MATCH($C8,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>240000</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="41">
         <f t="array" ref="H8">IF($D8="","",$D8*INDEX([1]Допущения!$C$25:$G$30,MATCH($C8,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>400000</v>
       </c>
-      <c r="I8" s="75">
+      <c r="I8" s="41">
         <f t="array" ref="I8">IF($D8="","",$D8*INDEX([1]Допущения!$C$25:$G$30,MATCH($C8,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>560000</v>
       </c>
-      <c r="J8" s="75">
-        <f>SUM(E8:I8)</f>
+      <c r="J8" s="41">
+        <f t="shared" si="0"/>
         <v>1320000</v>
       </c>
-      <c r="K8" s="82"/>
-      <c r="L8" s="81" t="s">
+      <c r="K8" s="48"/>
+      <c r="L8" s="47" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9" s="49">
         <v>6000</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="41">
         <f t="array" ref="E9">IF($D9="","",$D9*INDEX([1]Допущения!$C$25:$G$30,MATCH($C9,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>6000</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="41">
         <f t="array" ref="F9">IF($D9="","",$D9*INDEX([1]Допущения!$C$25:$G$30,MATCH($C9,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>24000</v>
       </c>
-      <c r="G9" s="75">
+      <c r="G9" s="41">
         <f t="array" ref="G9">IF($D9="","",$D9*INDEX([1]Допущения!$C$25:$G$30,MATCH($C9,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>60000</v>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="41">
         <f t="array" ref="H9">IF($D9="","",$D9*INDEX([1]Допущения!$C$25:$G$30,MATCH($C9,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>100000</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="41">
         <f t="array" ref="I9">IF($D9="","",$D9*INDEX([1]Допущения!$C$25:$G$30,MATCH($C9,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>140000</v>
       </c>
-      <c r="J9" s="75">
-        <f>SUM(E9:I9)</f>
+      <c r="J9" s="41">
+        <f t="shared" si="0"/>
         <v>330000</v>
       </c>
-      <c r="K9" s="82"/>
-      <c r="L9" s="81" t="s">
+      <c r="K9" s="48"/>
+      <c r="L9" s="47" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="83">
+      <c r="D10" s="49">
         <v>12000</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="41">
         <f t="array" ref="E10">IF($D10="","",$D10*INDEX([1]Допущения!$C$25:$G$30,MATCH($C10,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="41">
         <f t="array" ref="F10">IF($D10="","",$D10*INDEX([1]Допущения!$C$25:$G$30,MATCH($C10,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>48000</v>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="41">
         <f t="array" ref="G10">IF($D10="","",$D10*INDEX([1]Допущения!$C$25:$G$30,MATCH($C10,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>120000</v>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="41">
         <f t="array" ref="H10">IF($D10="","",$D10*INDEX([1]Допущения!$C$25:$G$30,MATCH($C10,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>200000</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="41">
         <f t="array" ref="I10">IF($D10="","",$D10*INDEX([1]Допущения!$C$25:$G$30,MATCH($C10,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>280000</v>
       </c>
-      <c r="J10" s="75">
-        <f>SUM(E10:I10)</f>
+      <c r="J10" s="41">
+        <f t="shared" si="0"/>
         <v>660000</v>
       </c>
-      <c r="K10" s="82"/>
-      <c r="L10" s="81" t="s">
+      <c r="K10" s="48"/>
+      <c r="L10" s="47" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="83">
+      <c r="D11" s="49">
         <v>12000</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="41">
         <f t="array" ref="E11">IF($D11="","",$D11*INDEX([1]Допущения!$C$25:$G$30,MATCH($C11,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="41">
         <f t="array" ref="F11">IF($D11="","",$D11*INDEX([1]Допущения!$C$25:$G$30,MATCH($C11,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>48000</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="41">
         <f t="array" ref="G11">IF($D11="","",$D11*INDEX([1]Допущения!$C$25:$G$30,MATCH($C11,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>120000</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="41">
         <f t="array" ref="H11">IF($D11="","",$D11*INDEX([1]Допущения!$C$25:$G$30,MATCH($C11,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>200000</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="41">
         <f t="array" ref="I11">IF($D11="","",$D11*INDEX([1]Допущения!$C$25:$G$30,MATCH($C11,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>280000</v>
       </c>
-      <c r="J11" s="75">
-        <f>SUM(E11:I11)</f>
+      <c r="J11" s="41">
+        <f t="shared" si="0"/>
         <v>660000</v>
       </c>
-      <c r="K11" s="82"/>
-      <c r="L11" s="81" t="s">
+      <c r="K11" s="48"/>
+      <c r="L11" s="47" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="49">
         <v>12000</v>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="41">
         <f t="array" ref="E12">IF($D12="","",$D12*INDEX([1]Допущения!$C$25:$G$30,MATCH($C12,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="41">
         <f t="array" ref="F12">IF($D12="","",$D12*INDEX([1]Допущения!$C$25:$G$30,MATCH($C12,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>48000</v>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="41">
         <f t="array" ref="G12">IF($D12="","",$D12*INDEX([1]Допущения!$C$25:$G$30,MATCH($C12,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>120000</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="41">
         <f t="array" ref="H12">IF($D12="","",$D12*INDEX([1]Допущения!$C$25:$G$30,MATCH($C12,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>200000</v>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="41">
         <f t="array" ref="I12">IF($D12="","",$D12*INDEX([1]Допущения!$C$25:$G$30,MATCH($C12,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>280000</v>
       </c>
-      <c r="J12" s="75">
-        <f>SUM(E12:I12)</f>
+      <c r="J12" s="41">
+        <f t="shared" si="0"/>
         <v>660000</v>
       </c>
-      <c r="K12" s="82"/>
-      <c r="L12" s="81" t="s">
+      <c r="K12" s="48"/>
+      <c r="L12" s="47" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="84" t="s">
+      <c r="C13" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="83">
+      <c r="D13" s="49">
         <v>12000</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="41">
         <f t="array" ref="E13">IF($D13="","",$D13*INDEX([1]Допущения!$C$25:$G$30,MATCH($C13,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="41">
         <f t="array" ref="F13">IF($D13="","",$D13*INDEX([1]Допущения!$C$25:$G$30,MATCH($C13,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>12960</v>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="41">
         <f t="array" ref="G13">IF($D13="","",$D13*INDEX([1]Допущения!$C$25:$G$30,MATCH($C13,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>13996.800000000001</v>
       </c>
-      <c r="H13" s="75">
+      <c r="H13" s="41">
         <f t="array" ref="H13">IF($D13="","",$D13*INDEX([1]Допущения!$C$25:$G$30,MATCH($C13,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>15116.544000000002</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="41">
         <f t="array" ref="I13">IF($D13="","",$D13*INDEX([1]Допущения!$C$25:$G$30,MATCH($C13,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>16325.867520000003</v>
       </c>
-      <c r="J13" s="75">
-        <f>SUM(E13:I13)</f>
+      <c r="J13" s="41">
+        <f t="shared" si="0"/>
         <v>70399.211520000012</v>
       </c>
-      <c r="K13" s="82"/>
-      <c r="L13" s="81" t="s">
+      <c r="K13" s="48"/>
+      <c r="L13" s="47" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="74"/>
-      <c r="C14" s="84" t="s">
+      <c r="B14" s="40"/>
+      <c r="C14" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="83"/>
-      <c r="E14" s="75" t="str">
+      <c r="D14" s="49"/>
+      <c r="E14" s="41" t="str">
         <f t="array" ref="E14">IF($D14="","",$D14*INDEX([1]Допущения!$C$25:$G$30,MATCH($C14,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F14" s="75" t="str">
+      <c r="F14" s="41" t="str">
         <f t="array" ref="F14">IF($D14="","",$D14*INDEX([1]Допущения!$C$25:$G$30,MATCH($C14,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G14" s="75" t="str">
+      <c r="G14" s="41" t="str">
         <f t="array" ref="G14">IF($D14="","",$D14*INDEX([1]Допущения!$C$25:$G$30,MATCH($C14,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H14" s="75" t="str">
+      <c r="H14" s="41" t="str">
         <f t="array" ref="H14">IF($D14="","",$D14*INDEX([1]Допущения!$C$25:$G$30,MATCH($C14,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I14" s="75" t="str">
+      <c r="I14" s="41" t="str">
         <f t="array" ref="I14">IF($D14="","",$D14*INDEX([1]Допущения!$C$25:$G$30,MATCH($C14,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J14" s="75">
-        <f>SUM(E14:I14)</f>
+      <c r="J14" s="41">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="82"/>
-      <c r="L14" s="81" t="s">
+      <c r="K14" s="48"/>
+      <c r="L14" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="71">
-        <f>SUM(E7:E14)</f>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="37">
+        <f t="shared" ref="E15:J15" si="1">SUM(E7:E14)</f>
         <v>103000</v>
       </c>
-      <c r="F15" s="71">
-        <f>SUM(F7:F14)</f>
+      <c r="F15" s="37">
+        <f t="shared" si="1"/>
         <v>376960</v>
       </c>
-      <c r="G15" s="71">
-        <f>SUM(G7:G14)</f>
+      <c r="G15" s="37">
+        <f t="shared" si="1"/>
         <v>923996.8</v>
       </c>
-      <c r="H15" s="71">
-        <f>SUM(H7:H14)</f>
+      <c r="H15" s="37">
+        <f t="shared" si="1"/>
         <v>1531783.2106666667</v>
       </c>
-      <c r="I15" s="71">
-        <f>SUM(I7:I14)</f>
+      <c r="I15" s="37">
+        <f t="shared" si="1"/>
         <v>2139659.2008533329</v>
       </c>
-      <c r="J15" s="71">
-        <f>SUM(J7:J14)</f>
+      <c r="J15" s="37">
+        <f t="shared" si="1"/>
         <v>5075399.2115200004</v>
       </c>
-      <c r="K15" s="80">
+      <c r="K15" s="46">
         <f>IFERROR(J15/$J$51,0)</f>
         <v>8.6279667524121542E-2</v>
       </c>
-      <c r="L15" s="79"/>
+      <c r="L15" s="45"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="77"/>
+      <c r="C16" s="43"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="83">
+      <c r="D18" s="49">
         <v>14000</v>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="41">
         <f t="array" ref="E18">IF($D18="","",$D18*INDEX([1]Допущения!$C$25:$G$30,MATCH($C18,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>14000</v>
       </c>
-      <c r="F18" s="75">
+      <c r="F18" s="41">
         <f t="array" ref="F18">IF($D18="","",$D18*INDEX([1]Допущения!$C$25:$G$30,MATCH($C18,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>56000</v>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="41">
         <f t="array" ref="G18">IF($D18="","",$D18*INDEX([1]Допущения!$C$25:$G$30,MATCH($C18,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>140000</v>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="41">
         <f t="array" ref="H18">IF($D18="","",$D18*INDEX([1]Допущения!$C$25:$G$30,MATCH($C18,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>233333.33333333334</v>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="41">
         <f t="array" ref="I18">IF($D18="","",$D18*INDEX([1]Допущения!$C$25:$G$30,MATCH($C18,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>326666.66666666663</v>
       </c>
-      <c r="J18" s="75">
-        <f>SUM(E18:I18)</f>
+      <c r="J18" s="41">
+        <f t="shared" ref="J18:J23" si="2">SUM(E18:I18)</f>
         <v>770000</v>
       </c>
-      <c r="K18" s="82"/>
-      <c r="L18" s="81" t="s">
+      <c r="K18" s="48"/>
+      <c r="L18" s="47" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="84" t="s">
+      <c r="C19" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="83">
+      <c r="D19" s="49">
         <v>4800</v>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="41">
         <f t="array" ref="E19">IF($D19="","",$D19*INDEX([1]Допущения!$C$25:$G$30,MATCH($C19,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>4800</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="41">
         <f t="array" ref="F19">IF($D19="","",$D19*INDEX([1]Допущения!$C$25:$G$30,MATCH($C19,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>5184</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="41">
         <f t="array" ref="G19">IF($D19="","",$D19*INDEX([1]Допущения!$C$25:$G$30,MATCH($C19,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>5598.72</v>
       </c>
-      <c r="H19" s="75">
+      <c r="H19" s="41">
         <f t="array" ref="H19">IF($D19="","",$D19*INDEX([1]Допущения!$C$25:$G$30,MATCH($C19,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>6046.6176000000005</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="41">
         <f t="array" ref="I19">IF($D19="","",$D19*INDEX([1]Допущения!$C$25:$G$30,MATCH($C19,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>6530.3470080000016</v>
       </c>
-      <c r="J19" s="75">
-        <f>SUM(E19:I19)</f>
+      <c r="J19" s="41">
+        <f t="shared" si="2"/>
         <v>28159.684608000003</v>
       </c>
-      <c r="K19" s="82"/>
-      <c r="L19" s="81" t="s">
+      <c r="K19" s="48"/>
+      <c r="L19" s="47" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="84" t="s">
+      <c r="C20" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="83">
+      <c r="D20" s="49">
         <v>7200</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="41">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX([1]Допущения!$C$25:$G$30,MATCH($C20,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>7200</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="41">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX([1]Допущения!$C$25:$G$30,MATCH($C20,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>28800</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="41">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX([1]Допущения!$C$25:$G$30,MATCH($C20,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>72000</v>
       </c>
-      <c r="H20" s="75">
+      <c r="H20" s="41">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX([1]Допущения!$C$25:$G$30,MATCH($C20,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>120000.00000000001</v>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="41">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX([1]Допущения!$C$25:$G$30,MATCH($C20,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>168000</v>
       </c>
-      <c r="J20" s="75">
-        <f>SUM(E20:I20)</f>
+      <c r="J20" s="41">
+        <f t="shared" si="2"/>
         <v>396000</v>
       </c>
-      <c r="K20" s="82"/>
-      <c r="L20" s="81" t="s">
+      <c r="K20" s="48"/>
+      <c r="L20" s="47" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="83">
+      <c r="D21" s="49">
         <v>3000</v>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="41">
         <f t="array" ref="E21">IF($D21="","",$D21*INDEX([1]Допущения!$C$25:$G$30,MATCH($C21,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>3000</v>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="41">
         <f t="array" ref="F21">IF($D21="","",$D21*INDEX([1]Допущения!$C$25:$G$30,MATCH($C21,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>3240</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="41">
         <f t="array" ref="G21">IF($D21="","",$D21*INDEX([1]Допущения!$C$25:$G$30,MATCH($C21,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>3499.2000000000003</v>
       </c>
-      <c r="H21" s="75">
+      <c r="H21" s="41">
         <f t="array" ref="H21">IF($D21="","",$D21*INDEX([1]Допущения!$C$25:$G$30,MATCH($C21,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>3779.1360000000004</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="41">
         <f t="array" ref="I21">IF($D21="","",$D21*INDEX([1]Допущения!$C$25:$G$30,MATCH($C21,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>4081.4668800000009</v>
       </c>
-      <c r="J21" s="75">
-        <f>SUM(E21:I21)</f>
+      <c r="J21" s="41">
+        <f t="shared" si="2"/>
         <v>17599.802880000003</v>
       </c>
-      <c r="K21" s="82"/>
-      <c r="L21" s="81" t="s">
+      <c r="K21" s="48"/>
+      <c r="L21" s="47" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="83">
+      <c r="D22" s="49">
         <v>2400</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="41">
         <f t="array" ref="E22">IF($D22="","",$D22*INDEX([1]Допущения!$C$25:$G$30,MATCH($C22,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>2400</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="41">
         <f t="array" ref="F22">IF($D22="","",$D22*INDEX([1]Допущения!$C$25:$G$30,MATCH($C22,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>2592</v>
       </c>
-      <c r="G22" s="75">
+      <c r="G22" s="41">
         <f t="array" ref="G22">IF($D22="","",$D22*INDEX([1]Допущения!$C$25:$G$30,MATCH($C22,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>2799.36</v>
       </c>
-      <c r="H22" s="75">
+      <c r="H22" s="41">
         <f t="array" ref="H22">IF($D22="","",$D22*INDEX([1]Допущения!$C$25:$G$30,MATCH($C22,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>3023.3088000000002</v>
       </c>
-      <c r="I22" s="75">
+      <c r="I22" s="41">
         <f t="array" ref="I22">IF($D22="","",$D22*INDEX([1]Допущения!$C$25:$G$30,MATCH($C22,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>3265.1735040000008</v>
       </c>
-      <c r="J22" s="75">
-        <f>SUM(E22:I22)</f>
+      <c r="J22" s="41">
+        <f t="shared" si="2"/>
         <v>14079.842304000002</v>
       </c>
-      <c r="K22" s="82"/>
-      <c r="L22" s="81" t="s">
+      <c r="K22" s="48"/>
+      <c r="L22" s="47" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="74"/>
-      <c r="C23" s="84" t="s">
+      <c r="B23" s="40"/>
+      <c r="C23" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="83"/>
-      <c r="E23" s="75" t="str">
+      <c r="D23" s="49"/>
+      <c r="E23" s="41" t="str">
         <f t="array" ref="E23">IF($D23="","",$D23*INDEX([1]Допущения!$C$25:$G$30,MATCH($C23,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F23" s="75" t="str">
+      <c r="F23" s="41" t="str">
         <f t="array" ref="F23">IF($D23="","",$D23*INDEX([1]Допущения!$C$25:$G$30,MATCH($C23,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G23" s="75" t="str">
+      <c r="G23" s="41" t="str">
         <f t="array" ref="G23">IF($D23="","",$D23*INDEX([1]Допущения!$C$25:$G$30,MATCH($C23,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H23" s="75" t="str">
+      <c r="H23" s="41" t="str">
         <f t="array" ref="H23">IF($D23="","",$D23*INDEX([1]Допущения!$C$25:$G$30,MATCH($C23,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I23" s="75" t="str">
+      <c r="I23" s="41" t="str">
         <f t="array" ref="I23">IF($D23="","",$D23*INDEX([1]Допущения!$C$25:$G$30,MATCH($C23,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J23" s="75">
-        <f>SUM(E23:I23)</f>
+      <c r="J23" s="41">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K23" s="82"/>
-      <c r="L23" s="81" t="s">
+      <c r="K23" s="48"/>
+      <c r="L23" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="71">
-        <f>SUM(E18:E23)</f>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="37">
+        <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
         <v>31400</v>
       </c>
-      <c r="F24" s="71">
-        <f>SUM(F18:F23)</f>
+      <c r="F24" s="37">
+        <f t="shared" si="3"/>
         <v>95816</v>
       </c>
-      <c r="G24" s="71">
-        <f>SUM(G18:G23)</f>
+      <c r="G24" s="37">
+        <f t="shared" si="3"/>
         <v>223897.28</v>
       </c>
-      <c r="H24" s="71">
-        <f>SUM(H18:H23)</f>
+      <c r="H24" s="37">
+        <f t="shared" si="3"/>
         <v>366182.39573333337</v>
       </c>
-      <c r="I24" s="71">
-        <f>SUM(I18:I23)</f>
+      <c r="I24" s="37">
+        <f t="shared" si="3"/>
         <v>508543.65405866667</v>
       </c>
-      <c r="J24" s="71">
-        <f>SUM(J18:J23)</f>
+      <c r="J24" s="37">
+        <f t="shared" si="3"/>
         <v>1225839.3297919999</v>
       </c>
-      <c r="K24" s="80">
+      <c r="K24" s="46">
         <f>IFERROR(J24/$J$51,0)</f>
         <v>2.0838756796191175E-2</v>
       </c>
-      <c r="L24" s="79"/>
+      <c r="L24" s="45"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="77"/>
+      <c r="C25" s="43"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="69"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="84" t="s">
+      <c r="C27" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="83">
+      <c r="D27" s="49">
         <v>225000</v>
       </c>
-      <c r="E27" s="75">
+      <c r="E27" s="41">
         <f t="array" ref="E27">IF($D27="","",$D27*INDEX([1]Допущения!$C$25:$G$30,MATCH($C27,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>225000</v>
       </c>
-      <c r="F27" s="75">
+      <c r="F27" s="41">
         <f t="array" ref="F27">IF($D27="","",$D27*INDEX([1]Допущения!$C$25:$G$30,MATCH($C27,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>1404000</v>
       </c>
-      <c r="G27" s="75">
+      <c r="G27" s="41">
         <f t="array" ref="G27">IF($D27="","",$D27*INDEX([1]Допущения!$C$25:$G$30,MATCH($C27,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>4860000</v>
       </c>
-      <c r="H27" s="75">
+      <c r="H27" s="41">
         <f t="array" ref="H27">IF($D27="","",$D27*INDEX([1]Допущения!$C$25:$G$30,MATCH($C27,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>10080000</v>
       </c>
-      <c r="I27" s="75">
+      <c r="I27" s="41">
         <f t="array" ref="I27">IF($D27="","",$D27*INDEX([1]Допущения!$C$25:$G$30,MATCH($C27,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>15659999.999999998</v>
       </c>
-      <c r="J27" s="75">
+      <c r="J27" s="41">
         <f>SUM(E27:I27)</f>
         <v>32229000</v>
       </c>
-      <c r="K27" s="82"/>
-      <c r="L27" s="81" t="s">
+      <c r="K27" s="48"/>
+      <c r="L27" s="47" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="83">
+      <c r="D28" s="49">
         <v>12000</v>
       </c>
-      <c r="E28" s="75">
+      <c r="E28" s="41">
         <f t="array" ref="E28">IF($D28="","",$D28*INDEX([1]Допущения!$C$25:$G$30,MATCH($C28,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F28" s="75">
+      <c r="F28" s="41">
         <f t="array" ref="F28">IF($D28="","",$D28*INDEX([1]Допущения!$C$25:$G$30,MATCH($C28,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>72000</v>
       </c>
-      <c r="G28" s="75">
+      <c r="G28" s="41">
         <f t="array" ref="G28">IF($D28="","",$D28*INDEX([1]Допущения!$C$25:$G$30,MATCH($C28,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>240000</v>
       </c>
-      <c r="H28" s="75">
+      <c r="H28" s="41">
         <f t="array" ref="H28">IF($D28="","",$D28*INDEX([1]Допущения!$C$25:$G$30,MATCH($C28,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>480000</v>
       </c>
-      <c r="I28" s="75">
+      <c r="I28" s="41">
         <f t="array" ref="I28">IF($D28="","",$D28*INDEX([1]Допущения!$C$25:$G$30,MATCH($C28,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>720000</v>
       </c>
-      <c r="J28" s="75">
+      <c r="J28" s="41">
         <f>SUM(E28:I28)</f>
         <v>1524000</v>
       </c>
-      <c r="K28" s="82"/>
-      <c r="L28" s="81" t="s">
+      <c r="K28" s="48"/>
+      <c r="L28" s="47" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="84" t="s">
+      <c r="C29" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="49">
         <v>9000</v>
       </c>
-      <c r="E29" s="75">
+      <c r="E29" s="41">
         <f t="array" ref="E29">IF($D29="","",$D29*INDEX([1]Допущения!$C$25:$G$30,MATCH($C29,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>9000</v>
       </c>
-      <c r="F29" s="75">
+      <c r="F29" s="41">
         <f t="array" ref="F29">IF($D29="","",$D29*INDEX([1]Допущения!$C$25:$G$30,MATCH($C29,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>54000</v>
       </c>
-      <c r="G29" s="75">
+      <c r="G29" s="41">
         <f t="array" ref="G29">IF($D29="","",$D29*INDEX([1]Допущения!$C$25:$G$30,MATCH($C29,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>180000</v>
       </c>
-      <c r="H29" s="75">
+      <c r="H29" s="41">
         <f t="array" ref="H29">IF($D29="","",$D29*INDEX([1]Допущения!$C$25:$G$30,MATCH($C29,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>360000</v>
       </c>
-      <c r="I29" s="75">
+      <c r="I29" s="41">
         <f t="array" ref="I29">IF($D29="","",$D29*INDEX([1]Допущения!$C$25:$G$30,MATCH($C29,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>540000</v>
       </c>
-      <c r="J29" s="75">
+      <c r="J29" s="41">
         <f>SUM(E29:I29)</f>
         <v>1143000</v>
       </c>
-      <c r="K29" s="82"/>
-      <c r="L29" s="81" t="s">
+      <c r="K29" s="48"/>
+      <c r="L29" s="47" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="84" t="s">
+      <c r="C30" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="83">
+      <c r="D30" s="49">
         <v>30000</v>
       </c>
-      <c r="E30" s="75">
+      <c r="E30" s="41">
         <f t="array" ref="E30">IF($D30="","",$D30*INDEX([1]Допущения!$C$25:$G$30,MATCH($C30,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>30000</v>
       </c>
-      <c r="F30" s="75">
+      <c r="F30" s="41">
         <f t="array" ref="F30">IF($D30="","",$D30*INDEX([1]Допущения!$C$25:$G$30,MATCH($C30,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>180000</v>
       </c>
-      <c r="G30" s="75">
+      <c r="G30" s="41">
         <f t="array" ref="G30">IF($D30="","",$D30*INDEX([1]Допущения!$C$25:$G$30,MATCH($C30,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>600000</v>
       </c>
-      <c r="H30" s="75">
+      <c r="H30" s="41">
         <f t="array" ref="H30">IF($D30="","",$D30*INDEX([1]Допущения!$C$25:$G$30,MATCH($C30,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>1200000</v>
       </c>
-      <c r="I30" s="75">
+      <c r="I30" s="41">
         <f t="array" ref="I30">IF($D30="","",$D30*INDEX([1]Допущения!$C$25:$G$30,MATCH($C30,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>1800000</v>
       </c>
-      <c r="J30" s="75">
+      <c r="J30" s="41">
         <f>SUM(E30:I30)</f>
         <v>3810000</v>
       </c>
-      <c r="K30" s="82"/>
-      <c r="L30" s="81" t="s">
+      <c r="K30" s="48"/>
+      <c r="L30" s="47" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="74"/>
-      <c r="C31" s="84" t="s">
+      <c r="B31" s="40"/>
+      <c r="C31" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="75" t="str">
+      <c r="D31" s="49"/>
+      <c r="E31" s="41" t="str">
         <f t="array" ref="E31">IF($D31="","",$D31*INDEX([1]Допущения!$C$25:$G$30,MATCH($C31,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F31" s="75" t="str">
+      <c r="F31" s="41" t="str">
         <f t="array" ref="F31">IF($D31="","",$D31*INDEX([1]Допущения!$C$25:$G$30,MATCH($C31,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G31" s="75" t="str">
+      <c r="G31" s="41" t="str">
         <f t="array" ref="G31">IF($D31="","",$D31*INDEX([1]Допущения!$C$25:$G$30,MATCH($C31,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H31" s="75" t="str">
+      <c r="H31" s="41" t="str">
         <f t="array" ref="H31">IF($D31="","",$D31*INDEX([1]Допущения!$C$25:$G$30,MATCH($C31,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I31" s="75" t="str">
+      <c r="I31" s="41" t="str">
         <f t="array" ref="I31">IF($D31="","",$D31*INDEX([1]Допущения!$C$25:$G$30,MATCH($C31,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J31" s="75">
+      <c r="J31" s="41">
         <f>SUM(E31:I31)</f>
         <v>0</v>
       </c>
-      <c r="K31" s="82"/>
-      <c r="L31" s="81" t="s">
+      <c r="K31" s="48"/>
+      <c r="L31" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="71">
-        <f>SUM(E27:E31)</f>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="37">
+        <f t="shared" ref="E32:J32" si="4">SUM(E27:E31)</f>
         <v>276000</v>
       </c>
-      <c r="F32" s="71">
-        <f>SUM(F27:F31)</f>
+      <c r="F32" s="37">
+        <f t="shared" si="4"/>
         <v>1710000</v>
       </c>
-      <c r="G32" s="71">
-        <f>SUM(G27:G31)</f>
+      <c r="G32" s="37">
+        <f t="shared" si="4"/>
         <v>5880000</v>
       </c>
-      <c r="H32" s="71">
-        <f>SUM(H27:H31)</f>
+      <c r="H32" s="37">
+        <f t="shared" si="4"/>
         <v>12120000</v>
       </c>
-      <c r="I32" s="71">
-        <f>SUM(I27:I31)</f>
+      <c r="I32" s="37">
+        <f t="shared" si="4"/>
         <v>18720000</v>
       </c>
-      <c r="J32" s="71">
-        <f>SUM(J27:J31)</f>
+      <c r="J32" s="37">
+        <f t="shared" si="4"/>
         <v>38706000</v>
       </c>
-      <c r="K32" s="80">
+      <c r="K32" s="46">
         <f>IFERROR(J32/$J$51,0)</f>
         <v>0.6579858395392133</v>
       </c>
-      <c r="L32" s="79"/>
+      <c r="L32" s="45"/>
     </row>
     <row r="33" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="77"/>
+      <c r="C33" s="43"/>
     </row>
     <row r="34" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="69"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
     </row>
     <row r="35" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="84" t="s">
+      <c r="C35" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="83">
+      <c r="D35" s="49">
         <v>600000</v>
       </c>
-      <c r="E35" s="75">
+      <c r="E35" s="41">
         <f t="array" ref="E35">IF($D35="","",$D35*INDEX([1]Допущения!$C$25:$G$30,MATCH($C35,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>600000</v>
       </c>
-      <c r="F35" s="75">
+      <c r="F35" s="41">
         <f t="array" ref="F35">IF($D35="","",$D35*INDEX([1]Допущения!$C$25:$G$30,MATCH($C35,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>672000.00000000012</v>
       </c>
-      <c r="G35" s="75">
+      <c r="G35" s="41">
         <f t="array" ref="G35">IF($D35="","",$D35*INDEX([1]Допущения!$C$25:$G$30,MATCH($C35,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>752640.00000000012</v>
       </c>
-      <c r="H35" s="75">
+      <c r="H35" s="41">
         <f t="array" ref="H35">IF($D35="","",$D35*INDEX([1]Допущения!$C$25:$G$30,MATCH($C35,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>842956.80000000028</v>
       </c>
-      <c r="I35" s="75">
+      <c r="I35" s="41">
         <f t="array" ref="I35">IF($D35="","",$D35*INDEX([1]Допущения!$C$25:$G$30,MATCH($C35,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>944111.61600000039</v>
       </c>
-      <c r="J35" s="75">
+      <c r="J35" s="41">
         <f>SUM(E35:I35)</f>
         <v>3811708.4160000007</v>
       </c>
-      <c r="K35" s="82"/>
-      <c r="L35" s="81" t="s">
+      <c r="K35" s="48"/>
+      <c r="L35" s="47" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="74" t="s">
+      <c r="B36" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="C36" s="84" t="s">
+      <c r="C36" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36" s="49">
         <v>90000</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="41">
         <f t="array" ref="E36">IF($D36="","",$D36*INDEX([1]Допущения!$C$25:$G$30,MATCH($C36,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>90000</v>
       </c>
-      <c r="F36" s="75">
+      <c r="F36" s="41">
         <f t="array" ref="F36">IF($D36="","",$D36*INDEX([1]Допущения!$C$25:$G$30,MATCH($C36,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>100800.00000000001</v>
       </c>
-      <c r="G36" s="75">
+      <c r="G36" s="41">
         <f t="array" ref="G36">IF($D36="","",$D36*INDEX([1]Допущения!$C$25:$G$30,MATCH($C36,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>112896.00000000001</v>
       </c>
-      <c r="H36" s="75">
+      <c r="H36" s="41">
         <f t="array" ref="H36">IF($D36="","",$D36*INDEX([1]Допущения!$C$25:$G$30,MATCH($C36,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>126443.52000000003</v>
       </c>
-      <c r="I36" s="75">
+      <c r="I36" s="41">
         <f t="array" ref="I36">IF($D36="","",$D36*INDEX([1]Допущения!$C$25:$G$30,MATCH($C36,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>141616.74240000005</v>
       </c>
-      <c r="J36" s="75">
+      <c r="J36" s="41">
         <f>SUM(E36:I36)</f>
         <v>571756.26240000012</v>
       </c>
-      <c r="K36" s="82"/>
-      <c r="L36" s="81" t="s">
+      <c r="K36" s="48"/>
+      <c r="L36" s="47" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="74" t="s">
+      <c r="B37" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="84" t="s">
+      <c r="C37" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D37" s="83">
+      <c r="D37" s="49">
         <v>48000</v>
       </c>
-      <c r="E37" s="75">
+      <c r="E37" s="41">
         <f t="array" ref="E37">IF($D37="","",$D37*INDEX([1]Допущения!$C$25:$G$30,MATCH($C37,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>48000</v>
       </c>
-      <c r="F37" s="75">
+      <c r="F37" s="41">
         <f t="array" ref="F37">IF($D37="","",$D37*INDEX([1]Допущения!$C$25:$G$30,MATCH($C37,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>53760.000000000007</v>
       </c>
-      <c r="G37" s="75">
+      <c r="G37" s="41">
         <f t="array" ref="G37">IF($D37="","",$D37*INDEX([1]Допущения!$C$25:$G$30,MATCH($C37,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>60211.200000000012</v>
       </c>
-      <c r="H37" s="75">
+      <c r="H37" s="41">
         <f t="array" ref="H37">IF($D37="","",$D37*INDEX([1]Допущения!$C$25:$G$30,MATCH($C37,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>67436.544000000024</v>
       </c>
-      <c r="I37" s="75">
+      <c r="I37" s="41">
         <f t="array" ref="I37">IF($D37="","",$D37*INDEX([1]Допущения!$C$25:$G$30,MATCH($C37,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>75528.929280000026</v>
       </c>
-      <c r="J37" s="75">
+      <c r="J37" s="41">
         <f>SUM(E37:I37)</f>
         <v>304936.67328000005</v>
       </c>
-      <c r="K37" s="82"/>
-      <c r="L37" s="81" t="s">
+      <c r="K37" s="48"/>
+      <c r="L37" s="47" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="74" t="s">
+      <c r="B38" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="84" t="s">
+      <c r="C38" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="83">
+      <c r="D38" s="49">
         <v>150000</v>
       </c>
-      <c r="E38" s="75">
+      <c r="E38" s="41">
         <f t="array" ref="E38">IF($D38="","",$D38*INDEX([1]Допущения!$C$25:$G$30,MATCH($C38,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>150000</v>
       </c>
-      <c r="F38" s="75">
+      <c r="F38" s="41">
         <f t="array" ref="F38">IF($D38="","",$D38*INDEX([1]Допущения!$C$25:$G$30,MATCH($C38,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>168000.00000000003</v>
       </c>
-      <c r="G38" s="75">
+      <c r="G38" s="41">
         <f t="array" ref="G38">IF($D38="","",$D38*INDEX([1]Допущения!$C$25:$G$30,MATCH($C38,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>188160.00000000003</v>
       </c>
-      <c r="H38" s="75">
+      <c r="H38" s="41">
         <f t="array" ref="H38">IF($D38="","",$D38*INDEX([1]Допущения!$C$25:$G$30,MATCH($C38,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>210739.20000000007</v>
       </c>
-      <c r="I38" s="75">
+      <c r="I38" s="41">
         <f t="array" ref="I38">IF($D38="","",$D38*INDEX([1]Допущения!$C$25:$G$30,MATCH($C38,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>236027.9040000001</v>
       </c>
-      <c r="J38" s="75">
+      <c r="J38" s="41">
         <f>SUM(E38:I38)</f>
         <v>952927.10400000017</v>
       </c>
-      <c r="K38" s="82"/>
-      <c r="L38" s="81" t="s">
+      <c r="K38" s="48"/>
+      <c r="L38" s="47" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="74"/>
-      <c r="C39" s="84" t="s">
+      <c r="B39" s="40"/>
+      <c r="C39" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="83"/>
-      <c r="E39" s="75" t="str">
+      <c r="D39" s="49"/>
+      <c r="E39" s="41" t="str">
         <f t="array" ref="E39">IF($D39="","",$D39*INDEX([1]Допущения!$C$25:$G$30,MATCH($C39,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F39" s="75" t="str">
+      <c r="F39" s="41" t="str">
         <f t="array" ref="F39">IF($D39="","",$D39*INDEX([1]Допущения!$C$25:$G$30,MATCH($C39,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G39" s="75" t="str">
+      <c r="G39" s="41" t="str">
         <f t="array" ref="G39">IF($D39="","",$D39*INDEX([1]Допущения!$C$25:$G$30,MATCH($C39,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H39" s="75" t="str">
+      <c r="H39" s="41" t="str">
         <f t="array" ref="H39">IF($D39="","",$D39*INDEX([1]Допущения!$C$25:$G$30,MATCH($C39,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I39" s="75" t="str">
+      <c r="I39" s="41" t="str">
         <f t="array" ref="I39">IF($D39="","",$D39*INDEX([1]Допущения!$C$25:$G$30,MATCH($C39,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J39" s="75">
+      <c r="J39" s="41">
         <f>SUM(E39:I39)</f>
         <v>0</v>
       </c>
-      <c r="K39" s="82"/>
-      <c r="L39" s="81" t="s">
+      <c r="K39" s="48"/>
+      <c r="L39" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="72" t="s">
+      <c r="B40" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="71">
-        <f>SUM(E35:E39)</f>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="37">
+        <f t="shared" ref="E40:J40" si="5">SUM(E35:E39)</f>
         <v>888000</v>
       </c>
-      <c r="F40" s="71">
-        <f>SUM(F35:F39)</f>
+      <c r="F40" s="37">
+        <f t="shared" si="5"/>
         <v>994560.00000000012</v>
       </c>
-      <c r="G40" s="71">
-        <f>SUM(G35:G39)</f>
+      <c r="G40" s="37">
+        <f t="shared" si="5"/>
         <v>1113907.2000000002</v>
       </c>
-      <c r="H40" s="71">
-        <f>SUM(H35:H39)</f>
+      <c r="H40" s="37">
+        <f t="shared" si="5"/>
         <v>1247576.0640000002</v>
       </c>
-      <c r="I40" s="71">
-        <f>SUM(I35:I39)</f>
+      <c r="I40" s="37">
+        <f t="shared" si="5"/>
         <v>1397285.1916800006</v>
       </c>
-      <c r="J40" s="71">
-        <f>SUM(J35:J39)</f>
+      <c r="J40" s="37">
+        <f t="shared" si="5"/>
         <v>5641328.4556800006</v>
       </c>
-      <c r="K40" s="80">
+      <c r="K40" s="46">
         <f>IFERROR(J40/$J$51,0)</f>
         <v>9.5900228389062647E-2</v>
       </c>
-      <c r="L40" s="79"/>
+      <c r="L40" s="45"/>
     </row>
     <row r="41" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="77"/>
+      <c r="C41" s="43"/>
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="69"/>
-      <c r="K42" s="69"/>
-      <c r="L42" s="69"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
     </row>
     <row r="43" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="74" t="s">
+      <c r="B43" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="C43" s="84" t="s">
+      <c r="C43" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="83">
+      <c r="D43" s="49">
         <v>25000</v>
       </c>
-      <c r="E43" s="75">
+      <c r="E43" s="41">
         <f t="array" ref="E43">IF($D43="","",$D43*INDEX([1]Допущения!$C$25:$G$30,MATCH($C43,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>25000</v>
       </c>
-      <c r="F43" s="75">
+      <c r="F43" s="41">
         <f t="array" ref="F43">IF($D43="","",$D43*INDEX([1]Допущения!$C$25:$G$30,MATCH($C43,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>25000</v>
       </c>
-      <c r="G43" s="75">
+      <c r="G43" s="41">
         <f t="array" ref="G43">IF($D43="","",$D43*INDEX([1]Допущения!$C$25:$G$30,MATCH($C43,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>25000</v>
       </c>
-      <c r="H43" s="75">
+      <c r="H43" s="41">
         <f t="array" ref="H43">IF($D43="","",$D43*INDEX([1]Допущения!$C$25:$G$30,MATCH($C43,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>25000</v>
       </c>
-      <c r="I43" s="75">
+      <c r="I43" s="41">
         <f t="array" ref="I43">IF($D43="","",$D43*INDEX([1]Допущения!$C$25:$G$30,MATCH($C43,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>25000</v>
       </c>
-      <c r="J43" s="75">
+      <c r="J43" s="41">
         <f>SUM(E43:I43)</f>
         <v>125000</v>
       </c>
-      <c r="K43" s="82"/>
-      <c r="L43" s="81" t="s">
+      <c r="K43" s="48"/>
+      <c r="L43" s="47" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="74" t="s">
+      <c r="B44" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="C44" s="84" t="s">
+      <c r="C44" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="83">
+      <c r="D44" s="49">
         <v>15000</v>
       </c>
-      <c r="E44" s="75">
+      <c r="E44" s="41">
         <f t="array" ref="E44">IF($D44="","",$D44*INDEX([1]Допущения!$C$25:$G$30,MATCH($C44,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>15000</v>
       </c>
-      <c r="F44" s="75">
+      <c r="F44" s="41">
         <f t="array" ref="F44">IF($D44="","",$D44*INDEX([1]Допущения!$C$25:$G$30,MATCH($C44,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>16200.000000000002</v>
       </c>
-      <c r="G44" s="75">
+      <c r="G44" s="41">
         <f t="array" ref="G44">IF($D44="","",$D44*INDEX([1]Допущения!$C$25:$G$30,MATCH($C44,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>17496</v>
       </c>
-      <c r="H44" s="75">
+      <c r="H44" s="41">
         <f t="array" ref="H44">IF($D44="","",$D44*INDEX([1]Допущения!$C$25:$G$30,MATCH($C44,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>18895.680000000004</v>
       </c>
-      <c r="I44" s="75">
+      <c r="I44" s="41">
         <f t="array" ref="I44">IF($D44="","",$D44*INDEX([1]Допущения!$C$25:$G$30,MATCH($C44,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>20407.334400000003</v>
       </c>
-      <c r="J44" s="75">
+      <c r="J44" s="41">
         <f>SUM(E44:I44)</f>
         <v>87999.014400000015</v>
       </c>
-      <c r="K44" s="82"/>
-      <c r="L44" s="81" t="s">
+      <c r="K44" s="48"/>
+      <c r="L44" s="47" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="45" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="74" t="s">
+      <c r="B45" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="84" t="s">
+      <c r="C45" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="83">
+      <c r="D45" s="49">
         <v>20000</v>
       </c>
-      <c r="E45" s="75">
+      <c r="E45" s="41">
         <f t="array" ref="E45">IF($D45="","",$D45*INDEX([1]Допущения!$C$25:$G$30,MATCH($C45,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>20000</v>
       </c>
-      <c r="F45" s="75">
+      <c r="F45" s="41">
         <f t="array" ref="F45">IF($D45="","",$D45*INDEX([1]Допущения!$C$25:$G$30,MATCH($C45,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>20000</v>
       </c>
-      <c r="G45" s="75">
+      <c r="G45" s="41">
         <f t="array" ref="G45">IF($D45="","",$D45*INDEX([1]Допущения!$C$25:$G$30,MATCH($C45,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>20000</v>
       </c>
-      <c r="H45" s="75">
+      <c r="H45" s="41">
         <f t="array" ref="H45">IF($D45="","",$D45*INDEX([1]Допущения!$C$25:$G$30,MATCH($C45,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>20000</v>
       </c>
-      <c r="I45" s="75">
+      <c r="I45" s="41">
         <f t="array" ref="I45">IF($D45="","",$D45*INDEX([1]Допущения!$C$25:$G$30,MATCH($C45,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>20000</v>
       </c>
-      <c r="J45" s="75">
+      <c r="J45" s="41">
         <f>SUM(E45:I45)</f>
         <v>100000</v>
       </c>
-      <c r="K45" s="82"/>
-      <c r="L45" s="81" t="s">
+      <c r="K45" s="48"/>
+      <c r="L45" s="47" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="74" t="s">
+      <c r="B46" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="84" t="s">
+      <c r="C46" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="83">
+      <c r="D46" s="49">
         <v>30000</v>
       </c>
-      <c r="E46" s="75">
+      <c r="E46" s="41">
         <f t="array" ref="E46">IF($D46="","",$D46*INDEX([1]Допущения!$C$25:$G$30,MATCH($C46,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v>30000</v>
       </c>
-      <c r="F46" s="75">
+      <c r="F46" s="41">
         <f t="array" ref="F46">IF($D46="","",$D46*INDEX([1]Допущения!$C$25:$G$30,MATCH($C46,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v>33600</v>
       </c>
-      <c r="G46" s="75">
+      <c r="G46" s="41">
         <f t="array" ref="G46">IF($D46="","",$D46*INDEX([1]Допущения!$C$25:$G$30,MATCH($C46,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v>37632.000000000007</v>
       </c>
-      <c r="H46" s="75">
+      <c r="H46" s="41">
         <f t="array" ref="H46">IF($D46="","",$D46*INDEX([1]Допущения!$C$25:$G$30,MATCH($C46,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v>42147.840000000011</v>
       </c>
-      <c r="I46" s="75">
+      <c r="I46" s="41">
         <f t="array" ref="I46">IF($D46="","",$D46*INDEX([1]Допущения!$C$25:$G$30,MATCH($C46,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v>47205.580800000018</v>
       </c>
-      <c r="J46" s="75">
+      <c r="J46" s="41">
         <f>SUM(E46:I46)</f>
         <v>190585.42080000005</v>
       </c>
-      <c r="K46" s="82"/>
-      <c r="L46" s="81" t="s">
+      <c r="K46" s="48"/>
+      <c r="L46" s="47" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="47" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="74"/>
-      <c r="C47" s="84" t="s">
+      <c r="B47" s="40"/>
+      <c r="C47" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D47" s="83"/>
-      <c r="E47" s="75" t="str">
+      <c r="D47" s="49"/>
+      <c r="E47" s="41" t="str">
         <f t="array" ref="E47">IF($D47="","",$D47*INDEX([1]Допущения!$C$25:$G$30,MATCH($C47,[1]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F47" s="75" t="str">
+      <c r="F47" s="41" t="str">
         <f t="array" ref="F47">IF($D47="","",$D47*INDEX([1]Допущения!$C$25:$G$30,MATCH($C47,[1]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G47" s="75" t="str">
+      <c r="G47" s="41" t="str">
         <f t="array" ref="G47">IF($D47="","",$D47*INDEX([1]Допущения!$C$25:$G$30,MATCH($C47,[1]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H47" s="75" t="str">
+      <c r="H47" s="41" t="str">
         <f t="array" ref="H47">IF($D47="","",$D47*INDEX([1]Допущения!$C$25:$G$30,MATCH($C47,[1]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I47" s="75" t="str">
+      <c r="I47" s="41" t="str">
         <f t="array" ref="I47">IF($D47="","",$D47*INDEX([1]Допущения!$C$25:$G$30,MATCH($C47,[1]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J47" s="75">
+      <c r="J47" s="41">
         <f>SUM(E47:I47)</f>
         <v>0</v>
       </c>
-      <c r="K47" s="82"/>
-      <c r="L47" s="81" t="s">
+      <c r="K47" s="48"/>
+      <c r="L47" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="48" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="79"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="71">
-        <f>SUM(E43:E47)</f>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="37">
+        <f t="shared" ref="E48:J48" si="6">SUM(E43:E47)</f>
         <v>90000</v>
       </c>
-      <c r="F48" s="71">
-        <f>SUM(F43:F47)</f>
+      <c r="F48" s="37">
+        <f t="shared" si="6"/>
         <v>94800</v>
       </c>
-      <c r="G48" s="71">
-        <f>SUM(G43:G47)</f>
+      <c r="G48" s="37">
+        <f t="shared" si="6"/>
         <v>100128</v>
       </c>
-      <c r="H48" s="71">
-        <f>SUM(H43:H47)</f>
+      <c r="H48" s="37">
+        <f t="shared" si="6"/>
         <v>106043.52000000002</v>
       </c>
-      <c r="I48" s="71">
-        <f>SUM(I43:I47)</f>
+      <c r="I48" s="37">
+        <f t="shared" si="6"/>
         <v>112612.91520000002</v>
       </c>
-      <c r="J48" s="71">
-        <f>SUM(J43:J47)</f>
+      <c r="J48" s="37">
+        <f t="shared" si="6"/>
         <v>503584.43520000007</v>
       </c>
-      <c r="K48" s="80">
+      <c r="K48" s="46">
         <f>IFERROR(J48/$J$51,0)</f>
         <v>8.5607251427156673E-3</v>
       </c>
-      <c r="L48" s="79"/>
+      <c r="L48" s="45"/>
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="77"/>
+      <c r="C49" s="43"/>
     </row>
     <row r="50" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="64" t="s">
+      <c r="B50" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="C50" s="77"/>
-      <c r="E50" s="76">
+      <c r="C50" s="43"/>
+      <c r="E50" s="42">
         <f>(E15+E24+E32+E40+E48)*[1]Допущения!$C$17</f>
         <v>208260</v>
       </c>
-      <c r="F50" s="76">
+      <c r="F50" s="42">
         <f>(F15+F24+F32+F40+F48)*[1]Допущения!$C$17</f>
         <v>490820.39999999997</v>
       </c>
-      <c r="G50" s="76">
+      <c r="G50" s="42">
         <f>(G15+G24+G32+G40+G48)*[1]Допущения!$C$17</f>
         <v>1236289.392</v>
       </c>
-      <c r="H50" s="76">
+      <c r="H50" s="42">
         <f>(H15+H24+H32+H40+H48)*[1]Допущения!$C$17</f>
         <v>2305737.77856</v>
       </c>
-      <c r="I50" s="76">
+      <c r="I50" s="42">
         <f>(I15+I24+I32+I40+I48)*[1]Допущения!$C$17</f>
         <v>3431715.1442687991</v>
       </c>
-      <c r="J50" s="75">
+      <c r="J50" s="41">
         <f>SUM(E50:I50)</f>
         <v>7672822.7148287985</v>
       </c>
-      <c r="L50" s="78" t="s">
+      <c r="L50" s="44" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="72" t="s">
+      <c r="B51" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="C51" s="77"/>
-      <c r="E51" s="71">
+      <c r="C51" s="43"/>
+      <c r="E51" s="37">
         <f>E15+E24+E32+E40+E48+E50</f>
         <v>1596660</v>
       </c>
-      <c r="F51" s="71">
+      <c r="F51" s="37">
         <f>F15+F24+F32+F40+F48+F50</f>
         <v>3762956.4</v>
       </c>
-      <c r="G51" s="71">
+      <c r="G51" s="37">
         <f>G15+G24+G32+G40+G48+G50</f>
         <v>9478218.6720000003</v>
       </c>
-      <c r="H51" s="71">
+      <c r="H51" s="37">
         <f>H15+H24+H32+H40+H48+H50</f>
         <v>17677322.968960002</v>
       </c>
-      <c r="I51" s="71">
+      <c r="I51" s="37">
         <f>I15+I24+I32+I40+I48+I50</f>
         <v>26309816.106060795</v>
       </c>
-      <c r="J51" s="71">
+      <c r="J51" s="37">
         <f>SUM(E51:I51)</f>
         <v>58824974.147020802</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="70" t="s">
+      <c r="B52" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="69"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="69"/>
-      <c r="L52" s="69"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="74" t="s">
+      <c r="B53" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="E53" s="76">
+      <c r="E53" s="42">
         <f>(1-[1]Допущения!$C$20)*525600*[1]Допущения!$C$19*[1]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="F53" s="76">
+      <c r="F53" s="42">
         <f>(1-[1]Допущения!$C$20)*525600*[1]Допущения!$C$19*[1]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="G53" s="76">
+      <c r="G53" s="42">
         <f>(1-[1]Допущения!$C$20)*525600*[1]Допущения!$C$19*[1]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="H53" s="76">
+      <c r="H53" s="42">
         <f>(1-[1]Допущения!$C$20)*525600*[1]Допущения!$C$19*[1]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="I53" s="76">
+      <c r="I53" s="42">
         <f>(1-[1]Допущения!$C$20)*525600*[1]Допущения!$C$19*[1]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="J53" s="75">
+      <c r="J53" s="41">
         <f>SUM(E53:I53)</f>
         <v>3153599.9999996526</v>
       </c>
-      <c r="L53" s="61" t="s">
+      <c r="L53" s="33" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="72" t="s">
+      <c r="B54" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="E54" s="71">
+      <c r="E54" s="37">
         <f>E51+E53</f>
         <v>2227379.9999999306</v>
       </c>
-      <c r="F54" s="71">
+      <c r="F54" s="37">
         <f>F51+F53</f>
         <v>4393676.3999999305</v>
       </c>
-      <c r="G54" s="71">
+      <c r="G54" s="37">
         <f>G51+G53</f>
         <v>10108938.671999931</v>
       </c>
-      <c r="H54" s="71">
+      <c r="H54" s="37">
         <f>H51+H53</f>
         <v>18308042.968959931</v>
       </c>
-      <c r="I54" s="71">
+      <c r="I54" s="37">
         <f>I51+I53</f>
         <v>26940536.106060725</v>
       </c>
-      <c r="J54" s="71">
+      <c r="J54" s="37">
         <f>SUM(E54:I54)</f>
         <v>61978574.147020444</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="74" t="s">
+      <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="E55" s="73">
+      <c r="E55" s="39">
         <f>1/(1+[1]Допущения!$C$16)^0</f>
         <v>1</v>
       </c>
-      <c r="F55" s="73">
+      <c r="F55" s="39">
         <f>1/(1+[1]Допущения!$C$16)^1</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G55" s="73">
+      <c r="G55" s="39">
         <f>1/(1+[1]Допущения!$C$16)^2</f>
         <v>0.69444444444444442</v>
       </c>
-      <c r="H55" s="73">
+      <c r="H55" s="39">
         <f>1/(1+[1]Допущения!$C$16)^3</f>
         <v>0.57870370370370372</v>
       </c>
-      <c r="I55" s="73">
+      <c r="I55" s="39">
         <f>1/(1+[1]Допущения!$C$16)^4</f>
         <v>0.48225308641975312</v>
       </c>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="72" t="s">
+      <c r="B56" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="E56" s="71">
+      <c r="E56" s="37">
         <f>E54*E55</f>
         <v>2227379.9999999306</v>
       </c>
-      <c r="F56" s="71">
+      <c r="F56" s="37">
         <f>F54*F55</f>
         <v>3661396.9999999423</v>
       </c>
-      <c r="G56" s="71">
+      <c r="G56" s="37">
         <f>G54*G55</f>
         <v>7020096.2999999523</v>
       </c>
-      <c r="H56" s="71">
+      <c r="H56" s="37">
         <f>H54*H55</f>
         <v>10594932.273703665</v>
       </c>
-      <c r="I56" s="71">
+      <c r="I56" s="37">
         <f>I54*I55</f>
         <v>12992156.686950581</v>
       </c>
-      <c r="J56" s="71">
+      <c r="J56" s="37">
         <f>SUM(E56:I56)</f>
         <v>36495962.260654069</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="70" t="s">
+      <c r="B58" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="C58" s="69"/>
-      <c r="D58" s="69"/>
-      <c r="E58" s="69"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="69"/>
-      <c r="I58" s="69"/>
-      <c r="J58" s="69"/>
-      <c r="K58" s="69"/>
-      <c r="L58" s="69"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="64" t="s">
+      <c r="B59" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="68">
+      <c r="E59" s="84">
         <f>J51</f>
         <v>58824974.147020802</v>
       </c>
-      <c r="F59" s="62"/>
-      <c r="L59" s="61" t="s">
+      <c r="F59" s="72"/>
+      <c r="L59" s="33" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="64" t="s">
+      <c r="B60" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="68">
+      <c r="E60" s="84">
         <f>J54</f>
         <v>61978574.147020444</v>
       </c>
-      <c r="F60" s="62"/>
-      <c r="L60" s="61" t="s">
+      <c r="F60" s="72"/>
+      <c r="L60" s="33" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="64" t="s">
+      <c r="B61" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="68">
+      <c r="E61" s="84">
         <f>J56</f>
         <v>36495962.260654069</v>
       </c>
-      <c r="F61" s="62"/>
-      <c r="L61" s="61" t="s">
+      <c r="F61" s="72"/>
+      <c r="L61" s="33" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="64" t="s">
+      <c r="B62" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="68">
+      <c r="E62" s="84">
         <f>J51/5</f>
         <v>11764994.82940416</v>
       </c>
-      <c r="F62" s="62"/>
-      <c r="L62" s="61" t="s">
+      <c r="F62" s="72"/>
+      <c r="L62" s="33" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="63" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="64" t="s">
+      <c r="B63" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="68">
+      <c r="E63" s="84">
         <f>E15/12</f>
         <v>8583.3333333333339</v>
       </c>
-      <c r="F63" s="62"/>
-      <c r="L63" s="61" t="s">
+      <c r="F63" s="72"/>
+      <c r="L63" s="33" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="64" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="64" t="s">
+      <c r="B64" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="67" t="str">
+      <c r="E64" s="85" t="str">
         <f>IF(E15/12&lt;=[1]Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>В бюджете CFO</v>
       </c>
-      <c r="F64" s="62"/>
-      <c r="L64" s="61" t="s">
+      <c r="F64" s="72"/>
+      <c r="L64" s="33" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="65" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="64" t="s">
+      <c r="B65" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="66">
+      <c r="E65" s="86">
         <f>IFERROR(J51/SUM([1]Допущения!$C$8:$G$8),0)</f>
         <v>1.5439625760372915</v>
       </c>
-      <c r="F65" s="62"/>
-      <c r="L65" s="61" t="s">
+      <c r="F65" s="72"/>
+      <c r="L65" s="33" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="66" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="64" t="s">
+      <c r="B66" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="66">
+      <c r="E66" s="86">
         <f>IFERROR(I51/[1]Допущения!$G$7,0)</f>
         <v>7.5170903160173701</v>
       </c>
-      <c r="F66" s="62"/>
-      <c r="L66" s="61" t="s">
+      <c r="F66" s="72"/>
+      <c r="L66" s="33" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="67" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="64" t="s">
+      <c r="B67" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="65">
+      <c r="E67" s="71">
         <f>IFERROR(J51/SUM([1]Допущения!$C$10:$G$10),0)</f>
         <v>5.475656161874784E-2</v>
       </c>
-      <c r="F67" s="62"/>
-      <c r="L67" s="61" t="s">
+      <c r="F67" s="72"/>
+      <c r="L67" s="33" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="68" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="64" t="s">
+      <c r="B68" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="63">
+      <c r="E68" s="73">
         <f>IFERROR(J15/J51,0)</f>
         <v>8.6279667524121542E-2</v>
       </c>
-      <c r="F68" s="62"/>
-      <c r="L68" s="61" t="s">
+      <c r="F68" s="72"/>
+      <c r="L68" s="33" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="64" t="s">
+      <c r="B69" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="63">
+      <c r="E69" s="73">
         <f>IFERROR(J32/J51,0)</f>
         <v>0.6579858395392133</v>
       </c>
-      <c r="F69" s="62"/>
-      <c r="L69" s="61" t="s">
+      <c r="F69" s="72"/>
+      <c r="L69" s="33" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="64" t="s">
+      <c r="B70" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="63">
+      <c r="E70" s="73">
         <f>IFERROR(J40/J51,0)</f>
         <v>9.5900228389062647E-2</v>
       </c>
-      <c r="F70" s="62"/>
-      <c r="L70" s="61" t="s">
+      <c r="F70" s="72"/>
+      <c r="L70" s="33" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="G72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="55"/>
-      <c r="K72" s="55"/>
-      <c r="L72" s="55"/>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="75"/>
+      <c r="I72" s="75"/>
+      <c r="J72" s="75"/>
+      <c r="K72" s="75"/>
+      <c r="L72" s="75"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="59" t="s">
+      <c r="B73" s="76" t="s">
         <v>188</v>
       </c>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
-      <c r="J73" s="58"/>
-      <c r="K73" s="58"/>
-      <c r="L73" s="57"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
+      <c r="E73" s="77"/>
+      <c r="F73" s="77"/>
+      <c r="G73" s="77"/>
+      <c r="H73" s="77"/>
+      <c r="I73" s="77"/>
+      <c r="J73" s="77"/>
+      <c r="K73" s="77"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="56"/>
-      <c r="C74" s="55"/>
-      <c r="D74" s="55"/>
-      <c r="E74" s="55"/>
-      <c r="F74" s="55"/>
-      <c r="G74" s="55"/>
-      <c r="H74" s="55"/>
-      <c r="I74" s="55"/>
-      <c r="J74" s="55"/>
-      <c r="K74" s="55"/>
-      <c r="L74" s="54"/>
+      <c r="B74" s="79"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="75"/>
+      <c r="G74" s="75"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="75"/>
+      <c r="J74" s="75"/>
+      <c r="K74" s="75"/>
+      <c r="L74" s="80"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="53"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="52"/>
-      <c r="K75" s="52"/>
-      <c r="L75" s="51"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="82"/>
+      <c r="F75" s="82"/>
+      <c r="G75" s="82"/>
+      <c r="H75" s="82"/>
+      <c r="I75" s="82"/>
+      <c r="J75" s="82"/>
+      <c r="K75" s="82"/>
+      <c r="L75" s="83"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9854,11 +9856,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="B72:L72"/>
     <mergeCell ref="B73:L75"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="E60:F60"/>
@@ -9868,6 +9865,11 @@
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="B72:L72"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="C6:C51">
@@ -9884,1550 +9886,1550 @@
   <dimension ref="B2:L1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="50" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="50" customWidth="1"/>
-    <col min="3" max="3" width="16" style="50" customWidth="1"/>
-    <col min="4" max="4" width="15" style="50" customWidth="1"/>
-    <col min="5" max="10" width="14" style="50" customWidth="1"/>
-    <col min="11" max="11" width="10" style="50" customWidth="1"/>
-    <col min="12" max="12" width="46" style="50" customWidth="1"/>
-    <col min="13" max="26" width="8.7109375" style="50" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="50"/>
+    <col min="1" max="1" width="3" style="32" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="16" style="32" customWidth="1"/>
+    <col min="4" max="4" width="15" style="32" customWidth="1"/>
+    <col min="5" max="10" width="14" style="32" customWidth="1"/>
+    <col min="11" max="11" width="10" style="32" customWidth="1"/>
+    <col min="12" max="12" width="46" style="32" customWidth="1"/>
+    <col min="13" max="26" width="8.7109375" style="32" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="32"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="85" t="s">
+      <c r="G5" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="85" t="s">
+      <c r="H5" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="85" t="s">
+      <c r="I5" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="85" t="s">
+      <c r="J5" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="85" t="s">
+      <c r="K5" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="85" t="s">
+      <c r="L5" s="51" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="83">
+      <c r="D7" s="49">
         <v>30000</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="41">
         <f t="array" ref="E7">IF($D7="","",$D7*INDEX([2]Допущения!$C$25:$G$30,MATCH($C7,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>30000</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="41">
         <f t="array" ref="F7">IF($D7="","",$D7*INDEX([2]Допущения!$C$25:$G$30,MATCH($C7,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>120000</v>
       </c>
-      <c r="G7" s="75">
+      <c r="G7" s="41">
         <f t="array" ref="G7">IF($D7="","",$D7*INDEX([2]Допущения!$C$25:$G$30,MATCH($C7,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>300000</v>
       </c>
-      <c r="H7" s="75">
+      <c r="H7" s="41">
         <f t="array" ref="H7">IF($D7="","",$D7*INDEX([2]Допущения!$C$25:$G$30,MATCH($C7,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>500000.00000000006</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="41">
         <f t="array" ref="I7">IF($D7="","",$D7*INDEX([2]Допущения!$C$25:$G$30,MATCH($C7,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>700000</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="41">
         <f t="shared" ref="J7:J14" si="0">SUM(E7:I7)</f>
         <v>1650000</v>
       </c>
-      <c r="K7" s="82"/>
-      <c r="L7" s="81" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="47" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="83">
+      <c r="D8" s="49">
         <v>18000</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="41">
         <f t="array" ref="E8">IF($D8="","",$D8*INDEX([2]Допущения!$C$25:$G$30,MATCH($C8,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>18000</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="41">
         <f t="array" ref="F8">IF($D8="","",$D8*INDEX([2]Допущения!$C$25:$G$30,MATCH($C8,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>72000</v>
       </c>
-      <c r="G8" s="75">
+      <c r="G8" s="41">
         <f t="array" ref="G8">IF($D8="","",$D8*INDEX([2]Допущения!$C$25:$G$30,MATCH($C8,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>180000</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="41">
         <f t="array" ref="H8">IF($D8="","",$D8*INDEX([2]Допущения!$C$25:$G$30,MATCH($C8,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>300000</v>
       </c>
-      <c r="I8" s="75">
+      <c r="I8" s="41">
         <f t="array" ref="I8">IF($D8="","",$D8*INDEX([2]Допущения!$C$25:$G$30,MATCH($C8,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>420000</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="41">
         <f t="shared" si="0"/>
         <v>990000</v>
       </c>
-      <c r="K8" s="82"/>
-      <c r="L8" s="81" t="s">
+      <c r="K8" s="48"/>
+      <c r="L8" s="47" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9" s="49">
         <v>6000</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="41">
         <f t="array" ref="E9">IF($D9="","",$D9*INDEX([2]Допущения!$C$25:$G$30,MATCH($C9,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>6000</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="41">
         <f t="array" ref="F9">IF($D9="","",$D9*INDEX([2]Допущения!$C$25:$G$30,MATCH($C9,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>24000</v>
       </c>
-      <c r="G9" s="75">
+      <c r="G9" s="41">
         <f t="array" ref="G9">IF($D9="","",$D9*INDEX([2]Допущения!$C$25:$G$30,MATCH($C9,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>60000</v>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="41">
         <f t="array" ref="H9">IF($D9="","",$D9*INDEX([2]Допущения!$C$25:$G$30,MATCH($C9,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>100000</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="41">
         <f t="array" ref="I9">IF($D9="","",$D9*INDEX([2]Допущения!$C$25:$G$30,MATCH($C9,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>140000</v>
       </c>
-      <c r="J9" s="75">
+      <c r="J9" s="41">
         <f t="shared" si="0"/>
         <v>330000</v>
       </c>
-      <c r="K9" s="82"/>
-      <c r="L9" s="81" t="s">
+      <c r="K9" s="48"/>
+      <c r="L9" s="47" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="83">
+      <c r="D10" s="49">
         <v>15000</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="41">
         <f t="array" ref="E10">IF($D10="","",$D10*INDEX([2]Допущения!$C$25:$G$30,MATCH($C10,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>15000</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="41">
         <f t="array" ref="F10">IF($D10="","",$D10*INDEX([2]Допущения!$C$25:$G$30,MATCH($C10,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>60000</v>
       </c>
-      <c r="G10" s="75">
+      <c r="G10" s="41">
         <f t="array" ref="G10">IF($D10="","",$D10*INDEX([2]Допущения!$C$25:$G$30,MATCH($C10,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>150000</v>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="41">
         <f t="array" ref="H10">IF($D10="","",$D10*INDEX([2]Допущения!$C$25:$G$30,MATCH($C10,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>250000.00000000003</v>
       </c>
-      <c r="I10" s="75">
+      <c r="I10" s="41">
         <f t="array" ref="I10">IF($D10="","",$D10*INDEX([2]Допущения!$C$25:$G$30,MATCH($C10,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>350000</v>
       </c>
-      <c r="J10" s="75">
+      <c r="J10" s="41">
         <f t="shared" si="0"/>
         <v>825000</v>
       </c>
-      <c r="K10" s="82"/>
-      <c r="L10" s="81" t="s">
+      <c r="K10" s="48"/>
+      <c r="L10" s="47" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="74" t="s">
+      <c r="B11" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="83">
+      <c r="D11" s="49">
         <v>12000</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="41">
         <f t="array" ref="E11">IF($D11="","",$D11*INDEX([2]Допущения!$C$25:$G$30,MATCH($C11,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="41">
         <f t="array" ref="F11">IF($D11="","",$D11*INDEX([2]Допущения!$C$25:$G$30,MATCH($C11,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>48000</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="41">
         <f t="array" ref="G11">IF($D11="","",$D11*INDEX([2]Допущения!$C$25:$G$30,MATCH($C11,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>120000</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="41">
         <f t="array" ref="H11">IF($D11="","",$D11*INDEX([2]Допущения!$C$25:$G$30,MATCH($C11,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>200000</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="41">
         <f t="array" ref="I11">IF($D11="","",$D11*INDEX([2]Допущения!$C$25:$G$30,MATCH($C11,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>280000</v>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="41">
         <f t="shared" si="0"/>
         <v>660000</v>
       </c>
-      <c r="K11" s="82"/>
-      <c r="L11" s="81" t="s">
+      <c r="K11" s="48"/>
+      <c r="L11" s="47" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="49">
         <v>24000</v>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="41">
         <f t="array" ref="E12">IF($D12="","",$D12*INDEX([2]Допущения!$C$25:$G$30,MATCH($C12,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>24000</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="41">
         <f t="array" ref="F12">IF($D12="","",$D12*INDEX([2]Допущения!$C$25:$G$30,MATCH($C12,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>96000</v>
       </c>
-      <c r="G12" s="75">
+      <c r="G12" s="41">
         <f t="array" ref="G12">IF($D12="","",$D12*INDEX([2]Допущения!$C$25:$G$30,MATCH($C12,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>240000</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="41">
         <f t="array" ref="H12">IF($D12="","",$D12*INDEX([2]Допущения!$C$25:$G$30,MATCH($C12,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>400000</v>
       </c>
-      <c r="I12" s="75">
+      <c r="I12" s="41">
         <f t="array" ref="I12">IF($D12="","",$D12*INDEX([2]Допущения!$C$25:$G$30,MATCH($C12,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>560000</v>
       </c>
-      <c r="J12" s="75">
+      <c r="J12" s="41">
         <f t="shared" si="0"/>
         <v>1320000</v>
       </c>
-      <c r="K12" s="82"/>
-      <c r="L12" s="81" t="s">
+      <c r="K12" s="48"/>
+      <c r="L12" s="47" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="84" t="s">
+      <c r="C13" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="83">
+      <c r="D13" s="49">
         <v>18000</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="41">
         <f t="array" ref="E13">IF($D13="","",$D13*INDEX([2]Допущения!$C$25:$G$30,MATCH($C13,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>18000</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="41">
         <f t="array" ref="F13">IF($D13="","",$D13*INDEX([2]Допущения!$C$25:$G$30,MATCH($C13,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>19440</v>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="41">
         <f t="array" ref="G13">IF($D13="","",$D13*INDEX([2]Допущения!$C$25:$G$30,MATCH($C13,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>20995.200000000001</v>
       </c>
-      <c r="H13" s="75">
+      <c r="H13" s="41">
         <f t="array" ref="H13">IF($D13="","",$D13*INDEX([2]Допущения!$C$25:$G$30,MATCH($C13,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>22674.816000000003</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="41">
         <f t="array" ref="I13">IF($D13="","",$D13*INDEX([2]Допущения!$C$25:$G$30,MATCH($C13,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>24488.801280000007</v>
       </c>
-      <c r="J13" s="75">
+      <c r="J13" s="41">
         <f t="shared" si="0"/>
         <v>105598.81728000002</v>
       </c>
-      <c r="K13" s="82"/>
-      <c r="L13" s="81" t="s">
+      <c r="K13" s="48"/>
+      <c r="L13" s="47" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="74"/>
-      <c r="C14" s="84" t="s">
+      <c r="B14" s="40"/>
+      <c r="C14" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="83"/>
-      <c r="E14" s="75" t="str">
+      <c r="D14" s="49"/>
+      <c r="E14" s="41" t="str">
         <f t="array" ref="E14">IF($D14="","",$D14*INDEX([2]Допущения!$C$25:$G$30,MATCH($C14,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F14" s="75" t="str">
+      <c r="F14" s="41" t="str">
         <f t="array" ref="F14">IF($D14="","",$D14*INDEX([2]Допущения!$C$25:$G$30,MATCH($C14,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G14" s="75" t="str">
+      <c r="G14" s="41" t="str">
         <f t="array" ref="G14">IF($D14="","",$D14*INDEX([2]Допущения!$C$25:$G$30,MATCH($C14,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H14" s="75" t="str">
+      <c r="H14" s="41" t="str">
         <f t="array" ref="H14">IF($D14="","",$D14*INDEX([2]Допущения!$C$25:$G$30,MATCH($C14,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I14" s="75" t="str">
+      <c r="I14" s="41" t="str">
         <f t="array" ref="I14">IF($D14="","",$D14*INDEX([2]Допущения!$C$25:$G$30,MATCH($C14,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J14" s="75">
+      <c r="J14" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="82"/>
-      <c r="L14" s="81" t="s">
+      <c r="K14" s="48"/>
+      <c r="L14" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="71">
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="37">
         <f t="shared" ref="E15:J15" si="1">SUM(E7:E14)</f>
         <v>123000</v>
       </c>
-      <c r="F15" s="71">
+      <c r="F15" s="37">
         <f t="shared" si="1"/>
         <v>439440</v>
       </c>
-      <c r="G15" s="71">
+      <c r="G15" s="37">
         <f t="shared" si="1"/>
         <v>1070995.2</v>
       </c>
-      <c r="H15" s="71">
+      <c r="H15" s="37">
         <f t="shared" si="1"/>
         <v>1772674.8160000001</v>
       </c>
-      <c r="I15" s="71">
+      <c r="I15" s="37">
         <f t="shared" si="1"/>
         <v>2474488.8012799998</v>
       </c>
-      <c r="J15" s="71">
+      <c r="J15" s="37">
         <f t="shared" si="1"/>
         <v>5880598.8172800001</v>
       </c>
-      <c r="K15" s="80">
+      <c r="K15" s="46">
         <f>IFERROR(J15/$J$51,0)</f>
         <v>9.0625253474794887E-2</v>
       </c>
-      <c r="L15" s="79"/>
+      <c r="L15" s="45"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="77"/>
+      <c r="C16" s="43"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="83">
+      <c r="D18" s="49">
         <v>18000</v>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="41">
         <f t="array" ref="E18">IF($D18="","",$D18*INDEX([2]Допущения!$C$25:$G$30,MATCH($C18,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>18000</v>
       </c>
-      <c r="F18" s="75">
+      <c r="F18" s="41">
         <f t="array" ref="F18">IF($D18="","",$D18*INDEX([2]Допущения!$C$25:$G$30,MATCH($C18,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>72000</v>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="41">
         <f t="array" ref="G18">IF($D18="","",$D18*INDEX([2]Допущения!$C$25:$G$30,MATCH($C18,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>180000</v>
       </c>
-      <c r="H18" s="75">
+      <c r="H18" s="41">
         <f t="array" ref="H18">IF($D18="","",$D18*INDEX([2]Допущения!$C$25:$G$30,MATCH($C18,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>300000</v>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="41">
         <f t="array" ref="I18">IF($D18="","",$D18*INDEX([2]Допущения!$C$25:$G$30,MATCH($C18,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>420000</v>
       </c>
-      <c r="J18" s="75">
+      <c r="J18" s="41">
         <f t="shared" ref="J18:J23" si="2">SUM(E18:I18)</f>
         <v>990000</v>
       </c>
-      <c r="K18" s="82"/>
-      <c r="L18" s="81" t="s">
+      <c r="K18" s="48"/>
+      <c r="L18" s="47" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="84" t="s">
+      <c r="C19" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="83">
+      <c r="D19" s="49">
         <v>7200</v>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="41">
         <f t="array" ref="E19">IF($D19="","",$D19*INDEX([2]Допущения!$C$25:$G$30,MATCH($C19,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>7200</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="41">
         <f t="array" ref="F19">IF($D19="","",$D19*INDEX([2]Допущения!$C$25:$G$30,MATCH($C19,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>7776.0000000000009</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="41">
         <f t="array" ref="G19">IF($D19="","",$D19*INDEX([2]Допущения!$C$25:$G$30,MATCH($C19,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>8398.08</v>
       </c>
-      <c r="H19" s="75">
+      <c r="H19" s="41">
         <f t="array" ref="H19">IF($D19="","",$D19*INDEX([2]Допущения!$C$25:$G$30,MATCH($C19,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>9069.9264000000003</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="41">
         <f t="array" ref="I19">IF($D19="","",$D19*INDEX([2]Допущения!$C$25:$G$30,MATCH($C19,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>9795.5205120000028</v>
       </c>
-      <c r="J19" s="75">
+      <c r="J19" s="41">
         <f t="shared" si="2"/>
         <v>42239.526912000001</v>
       </c>
-      <c r="K19" s="82"/>
-      <c r="L19" s="81" t="s">
+      <c r="K19" s="48"/>
+      <c r="L19" s="47" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="84" t="s">
+      <c r="C20" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="83">
+      <c r="D20" s="49">
         <v>12000</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="41">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX([2]Допущения!$C$25:$G$30,MATCH($C20,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="41">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX([2]Допущения!$C$25:$G$30,MATCH($C20,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>48000</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="41">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX([2]Допущения!$C$25:$G$30,MATCH($C20,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>120000</v>
       </c>
-      <c r="H20" s="75">
+      <c r="H20" s="41">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX([2]Допущения!$C$25:$G$30,MATCH($C20,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>200000</v>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="41">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX([2]Допущения!$C$25:$G$30,MATCH($C20,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>280000</v>
       </c>
-      <c r="J20" s="75">
+      <c r="J20" s="41">
         <f t="shared" si="2"/>
         <v>660000</v>
       </c>
-      <c r="K20" s="82"/>
-      <c r="L20" s="81" t="s">
+      <c r="K20" s="48"/>
+      <c r="L20" s="47" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="83">
+      <c r="D21" s="49">
         <v>3000</v>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="41">
         <f t="array" ref="E21">IF($D21="","",$D21*INDEX([2]Допущения!$C$25:$G$30,MATCH($C21,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>3000</v>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="41">
         <f t="array" ref="F21">IF($D21="","",$D21*INDEX([2]Допущения!$C$25:$G$30,MATCH($C21,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>3240</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="41">
         <f t="array" ref="G21">IF($D21="","",$D21*INDEX([2]Допущения!$C$25:$G$30,MATCH($C21,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>3499.2000000000003</v>
       </c>
-      <c r="H21" s="75">
+      <c r="H21" s="41">
         <f t="array" ref="H21">IF($D21="","",$D21*INDEX([2]Допущения!$C$25:$G$30,MATCH($C21,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>3779.1360000000004</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="41">
         <f t="array" ref="I21">IF($D21="","",$D21*INDEX([2]Допущения!$C$25:$G$30,MATCH($C21,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>4081.4668800000009</v>
       </c>
-      <c r="J21" s="75">
+      <c r="J21" s="41">
         <f t="shared" si="2"/>
         <v>17599.802880000003</v>
       </c>
-      <c r="K21" s="82"/>
-      <c r="L21" s="81" t="s">
+      <c r="K21" s="48"/>
+      <c r="L21" s="47" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="83">
+      <c r="D22" s="49">
         <v>4800</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="41">
         <f t="array" ref="E22">IF($D22="","",$D22*INDEX([2]Допущения!$C$25:$G$30,MATCH($C22,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>4800</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="41">
         <f t="array" ref="F22">IF($D22="","",$D22*INDEX([2]Допущения!$C$25:$G$30,MATCH($C22,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>5184</v>
       </c>
-      <c r="G22" s="75">
+      <c r="G22" s="41">
         <f t="array" ref="G22">IF($D22="","",$D22*INDEX([2]Допущения!$C$25:$G$30,MATCH($C22,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>5598.72</v>
       </c>
-      <c r="H22" s="75">
+      <c r="H22" s="41">
         <f t="array" ref="H22">IF($D22="","",$D22*INDEX([2]Допущения!$C$25:$G$30,MATCH($C22,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>6046.6176000000005</v>
       </c>
-      <c r="I22" s="75">
+      <c r="I22" s="41">
         <f t="array" ref="I22">IF($D22="","",$D22*INDEX([2]Допущения!$C$25:$G$30,MATCH($C22,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>6530.3470080000016</v>
       </c>
-      <c r="J22" s="75">
+      <c r="J22" s="41">
         <f t="shared" si="2"/>
         <v>28159.684608000003</v>
       </c>
-      <c r="K22" s="82"/>
-      <c r="L22" s="81" t="s">
+      <c r="K22" s="48"/>
+      <c r="L22" s="47" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="40" t="s">
         <v>189</v>
       </c>
-      <c r="C23" s="84" t="s">
+      <c r="C23" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="83">
+      <c r="D23" s="49">
         <v>200000</v>
       </c>
-      <c r="E23" s="75">
+      <c r="E23" s="41">
         <f t="array" ref="E23">IF($D23="","",$D23*INDEX([2]Допущения!$C$25:$G$30,MATCH($C23,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>200000</v>
       </c>
-      <c r="F23" s="75">
+      <c r="F23" s="41">
         <f t="array" ref="F23">IF($D23="","",$D23*INDEX([2]Допущения!$C$25:$G$30,MATCH($C23,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>216000</v>
       </c>
-      <c r="G23" s="75">
+      <c r="G23" s="41">
         <f t="array" ref="G23">IF($D23="","",$D23*INDEX([2]Допущения!$C$25:$G$30,MATCH($C23,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>233280.00000000003</v>
       </c>
-      <c r="H23" s="75">
+      <c r="H23" s="41">
         <f t="array" ref="H23">IF($D23="","",$D23*INDEX([2]Допущения!$C$25:$G$30,MATCH($C23,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>251942.40000000002</v>
       </c>
-      <c r="I23" s="75">
+      <c r="I23" s="41">
         <f t="array" ref="I23">IF($D23="","",$D23*INDEX([2]Допущения!$C$25:$G$30,MATCH($C23,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>272097.79200000007</v>
       </c>
-      <c r="J23" s="75">
+      <c r="J23" s="41">
         <f t="shared" si="2"/>
         <v>1173320.192</v>
       </c>
-      <c r="K23" s="82"/>
-      <c r="L23" s="81" t="s">
+      <c r="K23" s="48"/>
+      <c r="L23" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="71">
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="37">
         <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
         <v>245000</v>
       </c>
-      <c r="F24" s="71">
+      <c r="F24" s="37">
         <f t="shared" si="3"/>
         <v>352200</v>
       </c>
-      <c r="G24" s="71">
+      <c r="G24" s="37">
         <f t="shared" si="3"/>
         <v>550776</v>
       </c>
-      <c r="H24" s="71">
+      <c r="H24" s="37">
         <f t="shared" si="3"/>
         <v>770838.08000000007</v>
       </c>
-      <c r="I24" s="71">
+      <c r="I24" s="37">
         <f t="shared" si="3"/>
         <v>992505.12639999995</v>
       </c>
-      <c r="J24" s="71">
+      <c r="J24" s="37">
         <f t="shared" si="3"/>
         <v>2911319.2064000005</v>
       </c>
-      <c r="K24" s="80">
+      <c r="K24" s="46">
         <f>IFERROR(J24/$J$51,0)</f>
         <v>4.4866016068083749E-2</v>
       </c>
-      <c r="L24" s="79"/>
+      <c r="L24" s="45"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="77"/>
+      <c r="C25" s="43"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="69"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="84" t="s">
+      <c r="C27" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="83">
+      <c r="D27" s="49">
         <v>225000</v>
       </c>
-      <c r="E27" s="75">
+      <c r="E27" s="41">
         <f t="array" ref="E27">IF($D27="","",$D27*INDEX([2]Допущения!$C$25:$G$30,MATCH($C27,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>225000</v>
       </c>
-      <c r="F27" s="75">
+      <c r="F27" s="41">
         <f t="array" ref="F27">IF($D27="","",$D27*INDEX([2]Допущения!$C$25:$G$30,MATCH($C27,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>1404000</v>
       </c>
-      <c r="G27" s="75">
+      <c r="G27" s="41">
         <f t="array" ref="G27">IF($D27="","",$D27*INDEX([2]Допущения!$C$25:$G$30,MATCH($C27,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>4860000</v>
       </c>
-      <c r="H27" s="75">
+      <c r="H27" s="41">
         <f t="array" ref="H27">IF($D27="","",$D27*INDEX([2]Допущения!$C$25:$G$30,MATCH($C27,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>10080000</v>
       </c>
-      <c r="I27" s="75">
+      <c r="I27" s="41">
         <f t="array" ref="I27">IF($D27="","",$D27*INDEX([2]Допущения!$C$25:$G$30,MATCH($C27,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>15659999.999999998</v>
       </c>
-      <c r="J27" s="75">
+      <c r="J27" s="41">
         <f t="shared" ref="J27:J31" si="4">SUM(E27:I27)</f>
         <v>32229000</v>
       </c>
-      <c r="K27" s="82"/>
-      <c r="L27" s="81" t="s">
+      <c r="K27" s="48"/>
+      <c r="L27" s="47" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="83">
+      <c r="D28" s="49">
         <v>12000</v>
       </c>
-      <c r="E28" s="75">
+      <c r="E28" s="41">
         <f t="array" ref="E28">IF($D28="","",$D28*INDEX([2]Допущения!$C$25:$G$30,MATCH($C28,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>12000</v>
       </c>
-      <c r="F28" s="75">
+      <c r="F28" s="41">
         <f t="array" ref="F28">IF($D28="","",$D28*INDEX([2]Допущения!$C$25:$G$30,MATCH($C28,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>72000</v>
       </c>
-      <c r="G28" s="75">
+      <c r="G28" s="41">
         <f t="array" ref="G28">IF($D28="","",$D28*INDEX([2]Допущения!$C$25:$G$30,MATCH($C28,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>240000</v>
       </c>
-      <c r="H28" s="75">
+      <c r="H28" s="41">
         <f t="array" ref="H28">IF($D28="","",$D28*INDEX([2]Допущения!$C$25:$G$30,MATCH($C28,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>480000</v>
       </c>
-      <c r="I28" s="75">
+      <c r="I28" s="41">
         <f t="array" ref="I28">IF($D28="","",$D28*INDEX([2]Допущения!$C$25:$G$30,MATCH($C28,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>720000</v>
       </c>
-      <c r="J28" s="75">
+      <c r="J28" s="41">
         <f t="shared" si="4"/>
         <v>1524000</v>
       </c>
-      <c r="K28" s="82"/>
-      <c r="L28" s="81" t="s">
+      <c r="K28" s="48"/>
+      <c r="L28" s="47" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="84" t="s">
+      <c r="C29" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="49">
         <v>9000</v>
       </c>
-      <c r="E29" s="75">
+      <c r="E29" s="41">
         <f t="array" ref="E29">IF($D29="","",$D29*INDEX([2]Допущения!$C$25:$G$30,MATCH($C29,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>9000</v>
       </c>
-      <c r="F29" s="75">
+      <c r="F29" s="41">
         <f t="array" ref="F29">IF($D29="","",$D29*INDEX([2]Допущения!$C$25:$G$30,MATCH($C29,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>54000</v>
       </c>
-      <c r="G29" s="75">
+      <c r="G29" s="41">
         <f t="array" ref="G29">IF($D29="","",$D29*INDEX([2]Допущения!$C$25:$G$30,MATCH($C29,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>180000</v>
       </c>
-      <c r="H29" s="75">
+      <c r="H29" s="41">
         <f t="array" ref="H29">IF($D29="","",$D29*INDEX([2]Допущения!$C$25:$G$30,MATCH($C29,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>360000</v>
       </c>
-      <c r="I29" s="75">
+      <c r="I29" s="41">
         <f t="array" ref="I29">IF($D29="","",$D29*INDEX([2]Допущения!$C$25:$G$30,MATCH($C29,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>540000</v>
       </c>
-      <c r="J29" s="75">
+      <c r="J29" s="41">
         <f t="shared" si="4"/>
         <v>1143000</v>
       </c>
-      <c r="K29" s="82"/>
-      <c r="L29" s="81" t="s">
+      <c r="K29" s="48"/>
+      <c r="L29" s="47" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="84" t="s">
+      <c r="C30" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="83">
+      <c r="D30" s="49">
         <v>30000</v>
       </c>
-      <c r="E30" s="75">
+      <c r="E30" s="41">
         <f t="array" ref="E30">IF($D30="","",$D30*INDEX([2]Допущения!$C$25:$G$30,MATCH($C30,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>30000</v>
       </c>
-      <c r="F30" s="75">
+      <c r="F30" s="41">
         <f t="array" ref="F30">IF($D30="","",$D30*INDEX([2]Допущения!$C$25:$G$30,MATCH($C30,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>180000</v>
       </c>
-      <c r="G30" s="75">
+      <c r="G30" s="41">
         <f t="array" ref="G30">IF($D30="","",$D30*INDEX([2]Допущения!$C$25:$G$30,MATCH($C30,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>600000</v>
       </c>
-      <c r="H30" s="75">
+      <c r="H30" s="41">
         <f t="array" ref="H30">IF($D30="","",$D30*INDEX([2]Допущения!$C$25:$G$30,MATCH($C30,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>1200000</v>
       </c>
-      <c r="I30" s="75">
+      <c r="I30" s="41">
         <f t="array" ref="I30">IF($D30="","",$D30*INDEX([2]Допущения!$C$25:$G$30,MATCH($C30,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>1800000</v>
       </c>
-      <c r="J30" s="75">
+      <c r="J30" s="41">
         <f t="shared" si="4"/>
         <v>3810000</v>
       </c>
-      <c r="K30" s="82"/>
-      <c r="L30" s="81" t="s">
+      <c r="K30" s="48"/>
+      <c r="L30" s="47" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="74"/>
-      <c r="C31" s="84" t="s">
+      <c r="B31" s="40"/>
+      <c r="C31" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="75" t="str">
+      <c r="D31" s="49"/>
+      <c r="E31" s="41" t="str">
         <f t="array" ref="E31">IF($D31="","",$D31*INDEX([2]Допущения!$C$25:$G$30,MATCH($C31,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F31" s="75" t="str">
+      <c r="F31" s="41" t="str">
         <f t="array" ref="F31">IF($D31="","",$D31*INDEX([2]Допущения!$C$25:$G$30,MATCH($C31,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G31" s="75" t="str">
+      <c r="G31" s="41" t="str">
         <f t="array" ref="G31">IF($D31="","",$D31*INDEX([2]Допущения!$C$25:$G$30,MATCH($C31,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H31" s="75" t="str">
+      <c r="H31" s="41" t="str">
         <f t="array" ref="H31">IF($D31="","",$D31*INDEX([2]Допущения!$C$25:$G$30,MATCH($C31,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I31" s="75" t="str">
+      <c r="I31" s="41" t="str">
         <f t="array" ref="I31">IF($D31="","",$D31*INDEX([2]Допущения!$C$25:$G$30,MATCH($C31,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J31" s="75">
+      <c r="J31" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K31" s="82"/>
-      <c r="L31" s="81" t="s">
+      <c r="K31" s="48"/>
+      <c r="L31" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="71">
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="37">
         <f t="shared" ref="E32:J32" si="5">SUM(E27:E31)</f>
         <v>276000</v>
       </c>
-      <c r="F32" s="71">
+      <c r="F32" s="37">
         <f t="shared" si="5"/>
         <v>1710000</v>
       </c>
-      <c r="G32" s="71">
+      <c r="G32" s="37">
         <f t="shared" si="5"/>
         <v>5880000</v>
       </c>
-      <c r="H32" s="71">
+      <c r="H32" s="37">
         <f t="shared" si="5"/>
         <v>12120000</v>
       </c>
-      <c r="I32" s="71">
+      <c r="I32" s="37">
         <f t="shared" si="5"/>
         <v>18720000</v>
       </c>
-      <c r="J32" s="71">
+      <c r="J32" s="37">
         <f t="shared" si="5"/>
         <v>38706000</v>
       </c>
-      <c r="K32" s="80">
+      <c r="K32" s="46">
         <f>IFERROR(J32/$J$51,0)</f>
         <v>0.59649385547063627</v>
       </c>
-      <c r="L32" s="79"/>
+      <c r="L32" s="45"/>
     </row>
     <row r="33" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="77"/>
+      <c r="C33" s="43"/>
     </row>
     <row r="34" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="69"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
     </row>
     <row r="35" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="84" t="s">
+      <c r="C35" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="83">
+      <c r="D35" s="49">
         <v>960000</v>
       </c>
-      <c r="E35" s="75">
+      <c r="E35" s="41">
         <f t="array" ref="E35">IF($D35="","",$D35*INDEX([2]Допущения!$C$25:$G$30,MATCH($C35,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>960000</v>
       </c>
-      <c r="F35" s="75">
+      <c r="F35" s="41">
         <f t="array" ref="F35">IF($D35="","",$D35*INDEX([2]Допущения!$C$25:$G$30,MATCH($C35,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>1075200</v>
       </c>
-      <c r="G35" s="75">
+      <c r="G35" s="41">
         <f t="array" ref="G35">IF($D35="","",$D35*INDEX([2]Допущения!$C$25:$G$30,MATCH($C35,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>1204224.0000000002</v>
       </c>
-      <c r="H35" s="75">
+      <c r="H35" s="41">
         <f t="array" ref="H35">IF($D35="","",$D35*INDEX([2]Допущения!$C$25:$G$30,MATCH($C35,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>1348730.8800000004</v>
       </c>
-      <c r="I35" s="75">
+      <c r="I35" s="41">
         <f t="array" ref="I35">IF($D35="","",$D35*INDEX([2]Допущения!$C$25:$G$30,MATCH($C35,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>1510578.5856000006</v>
       </c>
-      <c r="J35" s="75">
+      <c r="J35" s="41">
         <f t="shared" ref="J35:J39" si="6">SUM(E35:I35)</f>
         <v>6098733.4656000016</v>
       </c>
-      <c r="K35" s="82"/>
-      <c r="L35" s="81" t="s">
+      <c r="K35" s="48"/>
+      <c r="L35" s="47" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="74" t="s">
+      <c r="B36" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="C36" s="84" t="s">
+      <c r="C36" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36" s="49">
         <v>120000</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="41">
         <f t="array" ref="E36">IF($D36="","",$D36*INDEX([2]Допущения!$C$25:$G$30,MATCH($C36,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>120000</v>
       </c>
-      <c r="F36" s="75">
+      <c r="F36" s="41">
         <f t="array" ref="F36">IF($D36="","",$D36*INDEX([2]Допущения!$C$25:$G$30,MATCH($C36,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>134400</v>
       </c>
-      <c r="G36" s="75">
+      <c r="G36" s="41">
         <f t="array" ref="G36">IF($D36="","",$D36*INDEX([2]Допущения!$C$25:$G$30,MATCH($C36,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>150528.00000000003</v>
       </c>
-      <c r="H36" s="75">
+      <c r="H36" s="41">
         <f t="array" ref="H36">IF($D36="","",$D36*INDEX([2]Допущения!$C$25:$G$30,MATCH($C36,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>168591.36000000004</v>
       </c>
-      <c r="I36" s="75">
+      <c r="I36" s="41">
         <f t="array" ref="I36">IF($D36="","",$D36*INDEX([2]Допущения!$C$25:$G$30,MATCH($C36,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>188822.32320000007</v>
       </c>
-      <c r="J36" s="75">
+      <c r="J36" s="41">
         <f t="shared" si="6"/>
         <v>762341.6832000002</v>
       </c>
-      <c r="K36" s="82"/>
-      <c r="L36" s="81" t="s">
+      <c r="K36" s="48"/>
+      <c r="L36" s="47" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="74" t="s">
+      <c r="B37" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="84" t="s">
+      <c r="C37" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D37" s="83">
+      <c r="D37" s="49">
         <v>96000</v>
       </c>
-      <c r="E37" s="75">
+      <c r="E37" s="41">
         <f t="array" ref="E37">IF($D37="","",$D37*INDEX([2]Допущения!$C$25:$G$30,MATCH($C37,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>96000</v>
       </c>
-      <c r="F37" s="75">
+      <c r="F37" s="41">
         <f t="array" ref="F37">IF($D37="","",$D37*INDEX([2]Допущения!$C$25:$G$30,MATCH($C37,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>107520.00000000001</v>
       </c>
-      <c r="G37" s="75">
+      <c r="G37" s="41">
         <f t="array" ref="G37">IF($D37="","",$D37*INDEX([2]Допущения!$C$25:$G$30,MATCH($C37,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>120422.40000000002</v>
       </c>
-      <c r="H37" s="75">
+      <c r="H37" s="41">
         <f t="array" ref="H37">IF($D37="","",$D37*INDEX([2]Допущения!$C$25:$G$30,MATCH($C37,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>134873.08800000005</v>
       </c>
-      <c r="I37" s="75">
+      <c r="I37" s="41">
         <f t="array" ref="I37">IF($D37="","",$D37*INDEX([2]Допущения!$C$25:$G$30,MATCH($C37,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>151057.85856000005</v>
       </c>
-      <c r="J37" s="75">
+      <c r="J37" s="41">
         <f t="shared" si="6"/>
         <v>609873.34656000009</v>
       </c>
-      <c r="K37" s="82"/>
-      <c r="L37" s="81" t="s">
+      <c r="K37" s="48"/>
+      <c r="L37" s="47" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="74" t="s">
+      <c r="B38" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="C38" s="84" t="s">
+      <c r="C38" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="83">
+      <c r="D38" s="49">
         <v>150000</v>
       </c>
-      <c r="E38" s="75">
+      <c r="E38" s="41">
         <f t="array" ref="E38">IF($D38="","",$D38*INDEX([2]Допущения!$C$25:$G$30,MATCH($C38,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>150000</v>
       </c>
-      <c r="F38" s="75">
+      <c r="F38" s="41">
         <f t="array" ref="F38">IF($D38="","",$D38*INDEX([2]Допущения!$C$25:$G$30,MATCH($C38,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>168000.00000000003</v>
       </c>
-      <c r="G38" s="75">
+      <c r="G38" s="41">
         <f t="array" ref="G38">IF($D38="","",$D38*INDEX([2]Допущения!$C$25:$G$30,MATCH($C38,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>188160.00000000003</v>
       </c>
-      <c r="H38" s="75">
+      <c r="H38" s="41">
         <f t="array" ref="H38">IF($D38="","",$D38*INDEX([2]Допущения!$C$25:$G$30,MATCH($C38,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>210739.20000000007</v>
       </c>
-      <c r="I38" s="75">
+      <c r="I38" s="41">
         <f t="array" ref="I38">IF($D38="","",$D38*INDEX([2]Допущения!$C$25:$G$30,MATCH($C38,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>236027.9040000001</v>
       </c>
-      <c r="J38" s="75">
+      <c r="J38" s="41">
         <f t="shared" si="6"/>
         <v>952927.10400000017</v>
       </c>
-      <c r="K38" s="82"/>
-      <c r="L38" s="81" t="s">
+      <c r="K38" s="48"/>
+      <c r="L38" s="47" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="74"/>
-      <c r="C39" s="84" t="s">
+      <c r="B39" s="40"/>
+      <c r="C39" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="83"/>
-      <c r="E39" s="75" t="str">
+      <c r="D39" s="49"/>
+      <c r="E39" s="41" t="str">
         <f t="array" ref="E39">IF($D39="","",$D39*INDEX([2]Допущения!$C$25:$G$30,MATCH($C39,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F39" s="75" t="str">
+      <c r="F39" s="41" t="str">
         <f t="array" ref="F39">IF($D39="","",$D39*INDEX([2]Допущения!$C$25:$G$30,MATCH($C39,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G39" s="75" t="str">
+      <c r="G39" s="41" t="str">
         <f t="array" ref="G39">IF($D39="","",$D39*INDEX([2]Допущения!$C$25:$G$30,MATCH($C39,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H39" s="75" t="str">
+      <c r="H39" s="41" t="str">
         <f t="array" ref="H39">IF($D39="","",$D39*INDEX([2]Допущения!$C$25:$G$30,MATCH($C39,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I39" s="75" t="str">
+      <c r="I39" s="41" t="str">
         <f t="array" ref="I39">IF($D39="","",$D39*INDEX([2]Допущения!$C$25:$G$30,MATCH($C39,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J39" s="75">
+      <c r="J39" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K39" s="82"/>
-      <c r="L39" s="81" t="s">
+      <c r="K39" s="48"/>
+      <c r="L39" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="72" t="s">
+      <c r="B40" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="71">
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="37">
         <f t="shared" ref="E40:J40" si="7">SUM(E35:E39)</f>
         <v>1326000</v>
       </c>
-      <c r="F40" s="71">
+      <c r="F40" s="37">
         <f t="shared" si="7"/>
         <v>1485120</v>
       </c>
-      <c r="G40" s="71">
+      <c r="G40" s="37">
         <f t="shared" si="7"/>
         <v>1663334.4000000004</v>
       </c>
-      <c r="H40" s="71">
+      <c r="H40" s="37">
         <f t="shared" si="7"/>
         <v>1862934.5280000004</v>
       </c>
-      <c r="I40" s="71">
+      <c r="I40" s="37">
         <f t="shared" si="7"/>
         <v>2086486.6713600007</v>
       </c>
-      <c r="J40" s="71">
+      <c r="J40" s="37">
         <f t="shared" si="7"/>
         <v>8423875.5993600022</v>
       </c>
-      <c r="K40" s="80">
+      <c r="K40" s="46">
         <f>IFERROR(J40/$J$51,0)</f>
         <v>0.12981940872906694</v>
       </c>
-      <c r="L40" s="79"/>
+      <c r="L40" s="45"/>
     </row>
     <row r="41" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="77"/>
+      <c r="C41" s="43"/>
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="69"/>
-      <c r="K42" s="69"/>
-      <c r="L42" s="69"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
     </row>
     <row r="43" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="74" t="s">
+      <c r="B43" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="C43" s="84" t="s">
+      <c r="C43" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="83">
+      <c r="D43" s="49">
         <v>25000</v>
       </c>
-      <c r="E43" s="75">
+      <c r="E43" s="41">
         <f t="array" ref="E43">IF($D43="","",$D43*INDEX([2]Допущения!$C$25:$G$30,MATCH($C43,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>25000</v>
       </c>
-      <c r="F43" s="75">
+      <c r="F43" s="41">
         <f t="array" ref="F43">IF($D43="","",$D43*INDEX([2]Допущения!$C$25:$G$30,MATCH($C43,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>25000</v>
       </c>
-      <c r="G43" s="75">
+      <c r="G43" s="41">
         <f t="array" ref="G43">IF($D43="","",$D43*INDEX([2]Допущения!$C$25:$G$30,MATCH($C43,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>25000</v>
       </c>
-      <c r="H43" s="75">
+      <c r="H43" s="41">
         <f t="array" ref="H43">IF($D43="","",$D43*INDEX([2]Допущения!$C$25:$G$30,MATCH($C43,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>25000</v>
       </c>
-      <c r="I43" s="75">
+      <c r="I43" s="41">
         <f t="array" ref="I43">IF($D43="","",$D43*INDEX([2]Допущения!$C$25:$G$30,MATCH($C43,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>25000</v>
       </c>
-      <c r="J43" s="75">
+      <c r="J43" s="41">
         <f t="shared" ref="J43:J47" si="8">SUM(E43:I43)</f>
         <v>125000</v>
       </c>
-      <c r="K43" s="82"/>
-      <c r="L43" s="81" t="s">
+      <c r="K43" s="48"/>
+      <c r="L43" s="47" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="74" t="s">
+      <c r="B44" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="C44" s="84" t="s">
+      <c r="C44" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="83">
+      <c r="D44" s="49">
         <v>15000</v>
       </c>
-      <c r="E44" s="75">
+      <c r="E44" s="41">
         <f t="array" ref="E44">IF($D44="","",$D44*INDEX([2]Допущения!$C$25:$G$30,MATCH($C44,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>15000</v>
       </c>
-      <c r="F44" s="75">
+      <c r="F44" s="41">
         <f t="array" ref="F44">IF($D44="","",$D44*INDEX([2]Допущения!$C$25:$G$30,MATCH($C44,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>16200.000000000002</v>
       </c>
-      <c r="G44" s="75">
+      <c r="G44" s="41">
         <f t="array" ref="G44">IF($D44="","",$D44*INDEX([2]Допущения!$C$25:$G$30,MATCH($C44,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>17496</v>
       </c>
-      <c r="H44" s="75">
+      <c r="H44" s="41">
         <f t="array" ref="H44">IF($D44="","",$D44*INDEX([2]Допущения!$C$25:$G$30,MATCH($C44,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>18895.680000000004</v>
       </c>
-      <c r="I44" s="75">
+      <c r="I44" s="41">
         <f t="array" ref="I44">IF($D44="","",$D44*INDEX([2]Допущения!$C$25:$G$30,MATCH($C44,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>20407.334400000003</v>
       </c>
-      <c r="J44" s="75">
+      <c r="J44" s="41">
         <f t="shared" si="8"/>
         <v>87999.014400000015</v>
       </c>
-      <c r="K44" s="82"/>
-      <c r="L44" s="81" t="s">
+      <c r="K44" s="48"/>
+      <c r="L44" s="47" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="45" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="74" t="s">
+      <c r="B45" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="84" t="s">
+      <c r="C45" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="83">
+      <c r="D45" s="49">
         <v>20000</v>
       </c>
-      <c r="E45" s="75">
+      <c r="E45" s="41">
         <f t="array" ref="E45">IF($D45="","",$D45*INDEX([2]Допущения!$C$25:$G$30,MATCH($C45,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>20000</v>
       </c>
-      <c r="F45" s="75">
+      <c r="F45" s="41">
         <f t="array" ref="F45">IF($D45="","",$D45*INDEX([2]Допущения!$C$25:$G$30,MATCH($C45,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>20000</v>
       </c>
-      <c r="G45" s="75">
+      <c r="G45" s="41">
         <f t="array" ref="G45">IF($D45="","",$D45*INDEX([2]Допущения!$C$25:$G$30,MATCH($C45,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>20000</v>
       </c>
-      <c r="H45" s="75">
+      <c r="H45" s="41">
         <f t="array" ref="H45">IF($D45="","",$D45*INDEX([2]Допущения!$C$25:$G$30,MATCH($C45,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>20000</v>
       </c>
-      <c r="I45" s="75">
+      <c r="I45" s="41">
         <f t="array" ref="I45">IF($D45="","",$D45*INDEX([2]Допущения!$C$25:$G$30,MATCH($C45,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>20000</v>
       </c>
-      <c r="J45" s="75">
+      <c r="J45" s="41">
         <f t="shared" si="8"/>
         <v>100000</v>
       </c>
-      <c r="K45" s="82"/>
-      <c r="L45" s="81" t="s">
+      <c r="K45" s="48"/>
+      <c r="L45" s="47" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="74" t="s">
+      <c r="B46" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="84" t="s">
+      <c r="C46" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="83">
+      <c r="D46" s="49">
         <v>30000</v>
       </c>
-      <c r="E46" s="75">
+      <c r="E46" s="41">
         <f t="array" ref="E46">IF($D46="","",$D46*INDEX([2]Допущения!$C$25:$G$30,MATCH($C46,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v>30000</v>
       </c>
-      <c r="F46" s="75">
+      <c r="F46" s="41">
         <f t="array" ref="F46">IF($D46="","",$D46*INDEX([2]Допущения!$C$25:$G$30,MATCH($C46,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v>33600</v>
       </c>
-      <c r="G46" s="75">
+      <c r="G46" s="41">
         <f t="array" ref="G46">IF($D46="","",$D46*INDEX([2]Допущения!$C$25:$G$30,MATCH($C46,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v>37632.000000000007</v>
       </c>
-      <c r="H46" s="75">
+      <c r="H46" s="41">
         <f t="array" ref="H46">IF($D46="","",$D46*INDEX([2]Допущения!$C$25:$G$30,MATCH($C46,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v>42147.840000000011</v>
       </c>
-      <c r="I46" s="75">
+      <c r="I46" s="41">
         <f t="array" ref="I46">IF($D46="","",$D46*INDEX([2]Допущения!$C$25:$G$30,MATCH($C46,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v>47205.580800000018</v>
       </c>
-      <c r="J46" s="75">
+      <c r="J46" s="41">
         <f t="shared" si="8"/>
         <v>190585.42080000005</v>
       </c>
-      <c r="K46" s="82"/>
-      <c r="L46" s="81" t="s">
+      <c r="K46" s="48"/>
+      <c r="L46" s="47" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="47" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="74"/>
-      <c r="C47" s="84" t="s">
+      <c r="B47" s="40"/>
+      <c r="C47" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D47" s="83"/>
-      <c r="E47" s="75" t="str">
+      <c r="D47" s="49"/>
+      <c r="E47" s="41" t="str">
         <f t="array" ref="E47">IF($D47="","",$D47*INDEX([2]Допущения!$C$25:$G$30,MATCH($C47,[2]Допущения!$B$25:$B$30,0),1))</f>
         <v/>
       </c>
-      <c r="F47" s="75" t="str">
+      <c r="F47" s="41" t="str">
         <f t="array" ref="F47">IF($D47="","",$D47*INDEX([2]Допущения!$C$25:$G$30,MATCH($C47,[2]Допущения!$B$25:$B$30,0),2))</f>
         <v/>
       </c>
-      <c r="G47" s="75" t="str">
+      <c r="G47" s="41" t="str">
         <f t="array" ref="G47">IF($D47="","",$D47*INDEX([2]Допущения!$C$25:$G$30,MATCH($C47,[2]Допущения!$B$25:$B$30,0),3))</f>
         <v/>
       </c>
-      <c r="H47" s="75" t="str">
+      <c r="H47" s="41" t="str">
         <f t="array" ref="H47">IF($D47="","",$D47*INDEX([2]Допущения!$C$25:$G$30,MATCH($C47,[2]Допущения!$B$25:$B$30,0),4))</f>
         <v/>
       </c>
-      <c r="I47" s="75" t="str">
+      <c r="I47" s="41" t="str">
         <f t="array" ref="I47">IF($D47="","",$D47*INDEX([2]Допущения!$C$25:$G$30,MATCH($C47,[2]Допущения!$B$25:$B$30,0),5))</f>
         <v/>
       </c>
-      <c r="J47" s="75">
+      <c r="J47" s="41">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K47" s="82"/>
-      <c r="L47" s="81" t="s">
+      <c r="K47" s="48"/>
+      <c r="L47" s="47" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="48" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="72" t="s">
+      <c r="B48" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="79"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="71">
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="37">
         <f t="shared" ref="E48:J48" si="9">SUM(E43:E47)</f>
         <v>90000</v>
       </c>
-      <c r="F48" s="71">
+      <c r="F48" s="37">
         <f t="shared" si="9"/>
         <v>94800</v>
       </c>
-      <c r="G48" s="71">
+      <c r="G48" s="37">
         <f t="shared" si="9"/>
         <v>100128</v>
       </c>
-      <c r="H48" s="71">
+      <c r="H48" s="37">
         <f t="shared" si="9"/>
         <v>106043.52000000002</v>
       </c>
-      <c r="I48" s="71">
+      <c r="I48" s="37">
         <f t="shared" si="9"/>
         <v>112612.91520000002</v>
       </c>
-      <c r="J48" s="71">
+      <c r="J48" s="37">
         <f t="shared" si="9"/>
         <v>503584.43520000007</v>
       </c>
-      <c r="K48" s="80">
+      <c r="K48" s="46">
         <f>IFERROR(J48/$J$51,0)</f>
         <v>7.7606836487224421E-3</v>
       </c>
-      <c r="L48" s="79"/>
+      <c r="L48" s="45"/>
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="77"/>
+      <c r="C49" s="43"/>
     </row>
     <row r="50" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="64" t="s">
+      <c r="B50" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="C50" s="77"/>
-      <c r="E50" s="76">
+      <c r="C50" s="43"/>
+      <c r="E50" s="42">
         <f>(E15+E24+E32+E40+E48)*[2]Допущения!$C$17</f>
         <v>309000</v>
       </c>
-      <c r="F50" s="76">
+      <c r="F50" s="42">
         <f>(F15+F24+F32+F40+F48)*[2]Допущения!$C$17</f>
         <v>612234</v>
       </c>
-      <c r="G50" s="76">
+      <c r="G50" s="42">
         <f>(G15+G24+G32+G40+G48)*[2]Допущения!$C$17</f>
         <v>1389785.0400000003</v>
       </c>
-      <c r="H50" s="76">
+      <c r="H50" s="42">
         <f>(H15+H24+H32+H40+H48)*[2]Допущения!$C$17</f>
         <v>2494873.6415999997</v>
       </c>
-      <c r="I50" s="76">
+      <c r="I50" s="42">
         <f>(I15+I24+I32+I40+I48)*[2]Допущения!$C$17</f>
         <v>3657914.0271359999</v>
       </c>
-      <c r="J50" s="75">
+      <c r="J50" s="41">
         <f t="shared" ref="J50:J51" si="10">SUM(E50:I50)</f>
         <v>8463806.7087359987</v>
       </c>
-      <c r="L50" s="78" t="s">
+      <c r="L50" s="44" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="72" t="s">
+      <c r="B51" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="C51" s="77"/>
-      <c r="E51" s="71">
+      <c r="C51" s="43"/>
+      <c r="E51" s="37">
         <f t="shared" ref="E51:I51" si="11">E15+E24+E32+E40+E48+E50</f>
         <v>2369000</v>
       </c>
-      <c r="F51" s="71">
+      <c r="F51" s="37">
         <f t="shared" si="11"/>
         <v>4693794</v>
       </c>
-      <c r="G51" s="71">
+      <c r="G51" s="37">
         <f t="shared" si="11"/>
         <v>10655018.640000002</v>
       </c>
-      <c r="H51" s="71">
+      <c r="H51" s="37">
         <f t="shared" si="11"/>
         <v>19127364.5856</v>
       </c>
-      <c r="I51" s="71">
+      <c r="I51" s="37">
         <f t="shared" si="11"/>
         <v>28044007.541376002</v>
       </c>
-      <c r="J51" s="71">
+      <c r="J51" s="37">
         <f t="shared" si="10"/>
         <v>64889184.766976006</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="70" t="s">
+      <c r="B52" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="C52" s="69"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="69"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="69"/>
-      <c r="L52" s="69"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="74" t="s">
+      <c r="B53" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="E53" s="76">
+      <c r="E53" s="42">
         <f>(1-[2]Допущения!$C$20)*525600*[2]Допущения!$C$19*[2]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="F53" s="76">
+      <c r="F53" s="42">
         <f>(1-[2]Допущения!$C$20)*525600*[2]Допущения!$C$19*[2]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="G53" s="76">
+      <c r="G53" s="42">
         <f>(1-[2]Допущения!$C$20)*525600*[2]Допущения!$C$19*[2]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="H53" s="76">
+      <c r="H53" s="42">
         <f>(1-[2]Допущения!$C$20)*525600*[2]Допущения!$C$19*[2]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="I53" s="76">
+      <c r="I53" s="42">
         <f>(1-[2]Допущения!$C$20)*525600*[2]Допущения!$C$19*[2]Допущения!$C$21</f>
         <v>630719.9999999305</v>
       </c>
-      <c r="J53" s="75">
+      <c r="J53" s="41">
         <f t="shared" ref="J53:J54" si="12">SUM(E53:I53)</f>
         <v>3153599.9999996526</v>
       </c>
@@ -11436,86 +11438,86 @@
       </c>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="72" t="s">
+      <c r="B54" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="E54" s="71">
+      <c r="E54" s="37">
         <f t="shared" ref="E54:I54" si="13">E51+E53</f>
         <v>2999719.9999999306</v>
       </c>
-      <c r="F54" s="71">
+      <c r="F54" s="37">
         <f t="shared" si="13"/>
         <v>5324513.9999999302</v>
       </c>
-      <c r="G54" s="71">
+      <c r="G54" s="37">
         <f t="shared" si="13"/>
         <v>11285738.639999934</v>
       </c>
-      <c r="H54" s="71">
+      <c r="H54" s="37">
         <f t="shared" si="13"/>
         <v>19758084.585599929</v>
       </c>
-      <c r="I54" s="71">
+      <c r="I54" s="37">
         <f t="shared" si="13"/>
         <v>28674727.541375931</v>
       </c>
-      <c r="J54" s="71">
+      <c r="J54" s="37">
         <f t="shared" si="12"/>
         <v>68042784.766975656</v>
       </c>
       <c r="L54" s="88"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="74" t="s">
+      <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="E55" s="73">
+      <c r="E55" s="39">
         <f>1/(1+[2]Допущения!$C$16)^0</f>
         <v>1</v>
       </c>
-      <c r="F55" s="73">
+      <c r="F55" s="39">
         <f>1/(1+[2]Допущения!$C$16)^1</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G55" s="73">
+      <c r="G55" s="39">
         <f>1/(1+[2]Допущения!$C$16)^2</f>
         <v>0.69444444444444442</v>
       </c>
-      <c r="H55" s="73">
+      <c r="H55" s="39">
         <f>1/(1+[2]Допущения!$C$16)^3</f>
         <v>0.57870370370370372</v>
       </c>
-      <c r="I55" s="73">
+      <c r="I55" s="39">
         <f>1/(1+[2]Допущения!$C$16)^4</f>
         <v>0.48225308641975312</v>
       </c>
       <c r="L55" s="88"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="72" t="s">
+      <c r="B56" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="E56" s="71">
+      <c r="E56" s="37">
         <f t="shared" ref="E56:I56" si="14">E54*E55</f>
         <v>2999719.9999999306</v>
       </c>
-      <c r="F56" s="71">
+      <c r="F56" s="37">
         <f t="shared" si="14"/>
         <v>4437094.9999999423</v>
       </c>
-      <c r="G56" s="71">
+      <c r="G56" s="37">
         <f t="shared" si="14"/>
         <v>7837318.4999999534</v>
       </c>
-      <c r="H56" s="71">
+      <c r="H56" s="37">
         <f t="shared" si="14"/>
         <v>11434076.727777736</v>
       </c>
-      <c r="I56" s="71">
+      <c r="I56" s="37">
         <f t="shared" si="14"/>
         <v>13828475.859074041</v>
       </c>
-      <c r="J56" s="71">
+      <c r="J56" s="37">
         <f>SUM(E56:I56)</f>
         <v>40536686.086851604</v>
       </c>
@@ -11525,232 +11527,232 @@
       <c r="L57" s="89"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="70" t="s">
+      <c r="B58" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="C58" s="69"/>
-      <c r="D58" s="69"/>
-      <c r="E58" s="69"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="69"/>
-      <c r="I58" s="69"/>
-      <c r="J58" s="69"/>
-      <c r="K58" s="69"/>
-      <c r="L58" s="69"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="64" t="s">
+      <c r="B59" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="68">
+      <c r="E59" s="84">
         <f>J51</f>
         <v>64889184.766976006</v>
       </c>
-      <c r="F59" s="62"/>
-      <c r="L59" s="61" t="s">
+      <c r="F59" s="72"/>
+      <c r="L59" s="33" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="64" t="s">
+      <c r="B60" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="68">
+      <c r="E60" s="84">
         <f>J54</f>
         <v>68042784.766975656</v>
       </c>
-      <c r="F60" s="62"/>
-      <c r="L60" s="61" t="s">
+      <c r="F60" s="72"/>
+      <c r="L60" s="33" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="64" t="s">
+      <c r="B61" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="68">
+      <c r="E61" s="84">
         <f>J56</f>
         <v>40536686.086851604</v>
       </c>
-      <c r="F61" s="62"/>
-      <c r="L61" s="61" t="s">
+      <c r="F61" s="72"/>
+      <c r="L61" s="33" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="64" t="s">
+      <c r="B62" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="68">
+      <c r="E62" s="84">
         <f>J51/5</f>
         <v>12977836.953395201</v>
       </c>
-      <c r="F62" s="62"/>
-      <c r="L62" s="61" t="s">
+      <c r="F62" s="72"/>
+      <c r="L62" s="33" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="63" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="64" t="s">
+      <c r="B63" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="68">
+      <c r="E63" s="84">
         <f>E15/12</f>
         <v>10250</v>
       </c>
-      <c r="F63" s="62"/>
-      <c r="L63" s="61" t="s">
+      <c r="F63" s="72"/>
+      <c r="L63" s="33" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="64" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="64" t="s">
+      <c r="B64" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="67" t="str">
+      <c r="E64" s="85" t="str">
         <f>IF(E15/12&lt;=[2]Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>ПРЕВЫШЕНИЕ бюджета</v>
       </c>
-      <c r="F64" s="62"/>
-      <c r="L64" s="61" t="s">
+      <c r="F64" s="72"/>
+      <c r="L64" s="33" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="65" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="64" t="s">
+      <c r="B65" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="66">
+      <c r="E65" s="86">
         <f>IFERROR(J51/SUM([2]Допущения!$C$8:$G$8),0)</f>
         <v>1.7031282091069817</v>
       </c>
-      <c r="F65" s="62"/>
-      <c r="L65" s="61" t="s">
+      <c r="F65" s="72"/>
+      <c r="L65" s="33" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="66" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="64" t="s">
+      <c r="B66" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="66">
+      <c r="E66" s="86">
         <f>IFERROR(I51/[2]Допущения!$G$7,0)</f>
         <v>8.0125735832502869</v>
       </c>
-      <c r="F66" s="62"/>
-      <c r="L66" s="61" t="s">
+      <c r="F66" s="72"/>
+      <c r="L66" s="33" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="67" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="64" t="s">
+      <c r="B67" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="65">
+      <c r="E67" s="71">
         <f>IFERROR(J51/SUM([2]Допущения!$C$10:$G$10),0)</f>
         <v>6.0401363461766736E-2</v>
       </c>
-      <c r="F67" s="62"/>
-      <c r="L67" s="61" t="s">
+      <c r="F67" s="72"/>
+      <c r="L67" s="33" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="68" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="64" t="s">
+      <c r="B68" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="63">
+      <c r="E68" s="73">
         <f>IFERROR(J15/J51,0)</f>
         <v>9.0625253474794887E-2</v>
       </c>
-      <c r="F68" s="62"/>
-      <c r="L68" s="61" t="s">
+      <c r="F68" s="72"/>
+      <c r="L68" s="33" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="64" t="s">
+      <c r="B69" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="63">
+      <c r="E69" s="73">
         <f>IFERROR(J32/J51,0)</f>
         <v>0.59649385547063627</v>
       </c>
-      <c r="F69" s="62"/>
-      <c r="L69" s="61" t="s">
+      <c r="F69" s="72"/>
+      <c r="L69" s="33" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="64" t="s">
+      <c r="B70" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="63">
+      <c r="E70" s="73">
         <f>IFERROR(J40/J51,0)</f>
         <v>0.12981940872906694</v>
       </c>
-      <c r="F70" s="62"/>
-      <c r="L70" s="61" t="s">
+      <c r="F70" s="72"/>
+      <c r="L70" s="33" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="G72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="55"/>
-      <c r="K72" s="55"/>
-      <c r="L72" s="55"/>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="75"/>
+      <c r="I72" s="75"/>
+      <c r="J72" s="75"/>
+      <c r="K72" s="75"/>
+      <c r="L72" s="75"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="59" t="s">
+      <c r="B73" s="76" t="s">
         <v>188</v>
       </c>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
-      <c r="J73" s="58"/>
-      <c r="K73" s="58"/>
-      <c r="L73" s="57"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
+      <c r="E73" s="77"/>
+      <c r="F73" s="77"/>
+      <c r="G73" s="77"/>
+      <c r="H73" s="77"/>
+      <c r="I73" s="77"/>
+      <c r="J73" s="77"/>
+      <c r="K73" s="77"/>
+      <c r="L73" s="78"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="56"/>
-      <c r="C74" s="55"/>
-      <c r="D74" s="55"/>
-      <c r="E74" s="55"/>
-      <c r="F74" s="55"/>
-      <c r="G74" s="55"/>
-      <c r="H74" s="55"/>
-      <c r="I74" s="55"/>
-      <c r="J74" s="55"/>
-      <c r="K74" s="55"/>
-      <c r="L74" s="54"/>
+      <c r="B74" s="79"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="75"/>
+      <c r="G74" s="75"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="75"/>
+      <c r="J74" s="75"/>
+      <c r="K74" s="75"/>
+      <c r="L74" s="80"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="53"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="52"/>
-      <c r="K75" s="52"/>
-      <c r="L75" s="51"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="82"/>
+      <c r="F75" s="82"/>
+      <c r="G75" s="82"/>
+      <c r="H75" s="82"/>
+      <c r="I75" s="82"/>
+      <c r="J75" s="82"/>
+      <c r="K75" s="82"/>
+      <c r="L75" s="83"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12679,6 +12681,12 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="L53:L57"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E62:F62"/>
     <mergeCell ref="E70:F70"/>
     <mergeCell ref="B72:L72"/>
     <mergeCell ref="B73:L75"/>
@@ -12688,12 +12696,6 @@
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="E69:F69"/>
-    <mergeCell ref="L53:L57"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="C6:C51">
